--- a/plantillas/65.xlsx
+++ b/plantillas/65.xlsx
@@ -14035,7 +14035,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         </is>
       </c>
       <c r="C466" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -23235,7 +23235,7 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         </is>
       </c>
       <c r="C541" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         </is>
       </c>
       <c r="C542" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         </is>
       </c>
       <c r="C558" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         </is>
       </c>
       <c r="C622" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -26275,7 +26275,7 @@
         </is>
       </c>
       <c r="C629" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         </is>
       </c>
       <c r="C633" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         </is>
       </c>
       <c r="C636" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         </is>
       </c>
       <c r="C649" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         </is>
       </c>
       <c r="C683" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         </is>
       </c>
       <c r="C698" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         </is>
       </c>
       <c r="C709" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         </is>
       </c>
       <c r="C742" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -28855,7 +28855,7 @@
         </is>
       </c>
       <c r="C758" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         </is>
       </c>
       <c r="C769" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         </is>
       </c>
       <c r="C771" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         </is>
       </c>
       <c r="C773" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         </is>
       </c>
       <c r="C793" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         </is>
       </c>
       <c r="C796" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -29755,7 +29755,7 @@
         </is>
       </c>
       <c r="C803" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         </is>
       </c>
       <c r="C808" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         </is>
       </c>
       <c r="C850" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         </is>
       </c>
       <c r="C852" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         </is>
       </c>
       <c r="C853" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         </is>
       </c>
       <c r="C862" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>19.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/65.xlsx
+++ b/plantillas/65.xlsx
@@ -59,7 +59,7 @@
     <definedName name="MARCA_45">Listas!$AV$2:$AV$12</definedName>
     <definedName name="MARCA_46">Listas!$AW$2:$AW$47</definedName>
     <definedName name="MARCA_47">Listas!$AX$2:$AX$7</definedName>
-    <definedName name="MARCA_48">Listas!$AY$2:$AY$9</definedName>
+    <definedName name="MARCA_48">Listas!$AY$2:$AY$8</definedName>
     <definedName name="MARCA_49">Listas!$AZ$2:$AZ$3</definedName>
     <definedName name="MARCA_50">Listas!$BA$2:$BA$4</definedName>
     <definedName name="MARCA_51">Listas!$BB$2:$BB$7</definedName>
@@ -677,11 +677,11 @@
       <c r="A3" s="5" t="n"/>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B3,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B3,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D3" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B3,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B3,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E3" s="8" t="n"/>
@@ -701,11 +701,11 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B4,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B4,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B4,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B4,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E4" s="8" t="n"/>
@@ -725,11 +725,11 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B5,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B5,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B5,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B5,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E5" s="8" t="n"/>
@@ -749,11 +749,11 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B6,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B6,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B6,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B6,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -768,11 +768,11 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B7,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B7,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B7,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B7,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -787,11 +787,11 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B8,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B8,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B8,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B8,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E8" s="8" t="n"/>
@@ -806,11 +806,11 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B9,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B9,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B9,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B9,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E9" s="8" t="n"/>
@@ -825,11 +825,11 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B10,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B10,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B10,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B10,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -844,11 +844,11 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B11,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B11,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B11,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B11,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -863,11 +863,11 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B12,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B12,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B12,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B12,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -882,11 +882,11 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B13,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B13,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B13,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B13,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E13" s="8" t="n"/>
@@ -901,11 +901,11 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B14,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B14,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B14,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B14,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E14" s="8" t="n"/>
@@ -920,11 +920,11 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B15,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B15,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B15,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B15,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E15" s="8" t="n"/>
@@ -939,11 +939,11 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B16,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B16,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B16,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B16,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -958,11 +958,11 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B17,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B17,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B17,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B17,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="8" t="n"/>
@@ -977,11 +977,11 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B18,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B18,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B18,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B18,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -996,11 +996,11 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B19,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B19,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B19,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B19,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -1015,11 +1015,11 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B20,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B20,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B20,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B20,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -1034,11 +1034,11 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B21,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B21,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B21,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B21,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="8" t="n"/>
@@ -1053,11 +1053,11 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B22,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B22,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B22,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B22,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="8" t="n"/>
@@ -1072,11 +1072,11 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B23,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B23,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B23,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B23,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="8" t="n"/>
@@ -1091,11 +1091,11 @@
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B24,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B24,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B24,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B24,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="8" t="n"/>
@@ -1110,11 +1110,11 @@
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B25,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B25,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B25,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B25,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="8" t="n"/>
@@ -1129,11 +1129,11 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B26,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B26,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B26,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B26,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -1148,11 +1148,11 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B27,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B27,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B27,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B27,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -1167,11 +1167,11 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B28,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B28,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B28,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B28,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -1186,11 +1186,11 @@
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B29,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B29,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B29,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B29,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -1205,11 +1205,11 @@
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B30,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B30,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B30,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B30,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -1224,11 +1224,11 @@
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B31,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B31,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B31,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B31,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -1243,11 +1243,11 @@
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B32,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B32,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B32,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B32,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -1262,11 +1262,11 @@
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B33,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B33,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B33,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B33,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -1281,11 +1281,11 @@
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B34,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B34,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B34,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B34,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -1300,11 +1300,11 @@
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B35,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B35,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B35,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B35,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -1319,11 +1319,11 @@
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B36,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B36,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B36,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B36,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -1338,11 +1338,11 @@
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B37,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B37,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B37,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B37,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -1357,11 +1357,11 @@
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B38,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B38,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B38,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B38,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E38" s="8" t="n"/>
@@ -1376,11 +1376,11 @@
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B39,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B39,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B39,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B39,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -1395,11 +1395,11 @@
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B40,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B40,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B40,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B40,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E40" s="8" t="n"/>
@@ -1414,11 +1414,11 @@
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B41,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B41,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B41,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B41,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -1433,11 +1433,11 @@
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B42,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B42,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B42,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B42,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -1452,11 +1452,11 @@
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B43,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B43,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B43,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B43,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -1471,11 +1471,11 @@
       <c r="A44" s="5" t="n"/>
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B44,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B44,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B44,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B44,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -1490,11 +1490,11 @@
       <c r="A45" s="5" t="n"/>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B45,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B45,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B45,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B45,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -1509,11 +1509,11 @@
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B46,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B46,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B46,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B46,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -1528,11 +1528,11 @@
       <c r="A47" s="5" t="n"/>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B47,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B47,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B47,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B47,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -1547,11 +1547,11 @@
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B48,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B48,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B48,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B48,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -1566,11 +1566,11 @@
       <c r="A49" s="5" t="n"/>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B49,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B49,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B49,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B49,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -1585,11 +1585,11 @@
       <c r="A50" s="5" t="n"/>
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B50,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B50,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B50,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B50,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -1604,11 +1604,11 @@
       <c r="A51" s="5" t="n"/>
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B51,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B51,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B51,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B51,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -1623,11 +1623,11 @@
       <c r="A52" s="5" t="n"/>
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B52,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B52,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D52" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B52,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B52,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E52" s="8" t="n"/>
@@ -1642,11 +1642,11 @@
       <c r="A53" s="5" t="n"/>
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B53,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B53,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D53" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B53,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B53,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E53" s="8" t="n"/>
@@ -1661,11 +1661,11 @@
       <c r="A54" s="5" t="n"/>
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B54,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B54,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D54" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B54,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B54,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -1680,11 +1680,11 @@
       <c r="A55" s="5" t="n"/>
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B55,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B55,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D55" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B55,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B55,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -1699,11 +1699,11 @@
       <c r="A56" s="5" t="n"/>
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B56,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B56,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D56" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B56,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B56,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E56" s="8" t="n"/>
@@ -1718,11 +1718,11 @@
       <c r="A57" s="5" t="n"/>
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B57,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B57,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D57" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B57,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B57,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E57" s="8" t="n"/>
@@ -1737,11 +1737,11 @@
       <c r="A58" s="5" t="n"/>
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B58,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B58,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D58" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B58,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B58,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -1756,11 +1756,11 @@
       <c r="A59" s="5" t="n"/>
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B59,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B59,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D59" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B59,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B59,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -1775,11 +1775,11 @@
       <c r="A60" s="5" t="n"/>
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B60,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B60,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D60" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B60,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B60,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -1794,11 +1794,11 @@
       <c r="A61" s="5" t="n"/>
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B61,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B61,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D61" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B61,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B61,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -1813,11 +1813,11 @@
       <c r="A62" s="5" t="n"/>
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B62,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B62,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D62" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B62,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B62,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -1832,11 +1832,11 @@
       <c r="A63" s="5" t="n"/>
       <c r="B63" s="5" t="n"/>
       <c r="C63" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B63,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B63,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D63" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B63,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B63,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -1851,11 +1851,11 @@
       <c r="A64" s="5" t="n"/>
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B64,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B64,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D64" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B64,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B64,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -1870,11 +1870,11 @@
       <c r="A65" s="5" t="n"/>
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B65,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B65,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D65" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B65,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B65,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -1889,11 +1889,11 @@
       <c r="A66" s="5" t="n"/>
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B66,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B66,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D66" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B66,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B66,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E66" s="8" t="n"/>
@@ -1908,11 +1908,11 @@
       <c r="A67" s="5" t="n"/>
       <c r="B67" s="5" t="n"/>
       <c r="C67" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B67,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B67,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D67" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B67,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B67,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -1927,11 +1927,11 @@
       <c r="A68" s="5" t="n"/>
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B68,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B68,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D68" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B68,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B68,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -1946,11 +1946,11 @@
       <c r="A69" s="5" t="n"/>
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B69,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B69,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D69" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B69,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B69,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -1965,11 +1965,11 @@
       <c r="A70" s="5" t="n"/>
       <c r="B70" s="5" t="n"/>
       <c r="C70" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B70,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B70,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D70" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B70,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B70,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -1984,11 +1984,11 @@
       <c r="A71" s="5" t="n"/>
       <c r="B71" s="5" t="n"/>
       <c r="C71" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B71,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B71,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D71" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B71,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B71,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -2003,11 +2003,11 @@
       <c r="A72" s="5" t="n"/>
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B72,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B72,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D72" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B72,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B72,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -2022,11 +2022,11 @@
       <c r="A73" s="5" t="n"/>
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B73,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B73,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D73" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B73,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B73,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -2041,11 +2041,11 @@
       <c r="A74" s="5" t="n"/>
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B74,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B74,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D74" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B74,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B74,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -2060,11 +2060,11 @@
       <c r="A75" s="5" t="n"/>
       <c r="B75" s="5" t="n"/>
       <c r="C75" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B75,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B75,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D75" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B75,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B75,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -2079,11 +2079,11 @@
       <c r="A76" s="5" t="n"/>
       <c r="B76" s="5" t="n"/>
       <c r="C76" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B76,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B76,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D76" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B76,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B76,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -2098,11 +2098,11 @@
       <c r="A77" s="5" t="n"/>
       <c r="B77" s="5" t="n"/>
       <c r="C77" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B77,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B77,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D77" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B77,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B77,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -2117,11 +2117,11 @@
       <c r="A78" s="5" t="n"/>
       <c r="B78" s="5" t="n"/>
       <c r="C78" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B78,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B78,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D78" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B78,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B78,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E78" s="8" t="n"/>
@@ -2136,11 +2136,11 @@
       <c r="A79" s="5" t="n"/>
       <c r="B79" s="5" t="n"/>
       <c r="C79" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B79,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B79,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D79" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B79,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B79,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E79" s="8" t="n"/>
@@ -2155,11 +2155,11 @@
       <c r="A80" s="5" t="n"/>
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B80,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B80,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D80" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B80,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B80,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -2174,11 +2174,11 @@
       <c r="A81" s="5" t="n"/>
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B81,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B81,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D81" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B81,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B81,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E81" s="8" t="n"/>
@@ -2193,11 +2193,11 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B82,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B82,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D82" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B82,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B82,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -2212,11 +2212,11 @@
       <c r="A83" s="5" t="n"/>
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B83,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B83,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D83" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B83,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B83,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -2231,11 +2231,11 @@
       <c r="A84" s="5" t="n"/>
       <c r="B84" s="5" t="n"/>
       <c r="C84" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B84,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B84,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D84" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B84,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B84,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -2250,11 +2250,11 @@
       <c r="A85" s="5" t="n"/>
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B85,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B85,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D85" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B85,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B85,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -2269,11 +2269,11 @@
       <c r="A86" s="5" t="n"/>
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B86,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B86,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D86" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B86,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B86,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -2288,11 +2288,11 @@
       <c r="A87" s="5" t="n"/>
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B87,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B87,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D87" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B87,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B87,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -2307,11 +2307,11 @@
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B88,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B88,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D88" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B88,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B88,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E88" s="8" t="n"/>
@@ -2326,11 +2326,11 @@
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B89,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B89,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D89" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B89,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B89,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E89" s="8" t="n"/>
@@ -2345,11 +2345,11 @@
       <c r="A90" s="5" t="n"/>
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B90,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B90,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D90" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B90,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B90,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E90" s="8" t="n"/>
@@ -2364,11 +2364,11 @@
       <c r="A91" s="5" t="n"/>
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B91,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B91,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D91" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B91,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B91,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -2383,11 +2383,11 @@
       <c r="A92" s="5" t="n"/>
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B92,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B92,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D92" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B92,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B92,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -2402,11 +2402,11 @@
       <c r="A93" s="5" t="n"/>
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B93,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B93,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D93" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B93,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B93,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -2421,11 +2421,11 @@
       <c r="A94" s="5" t="n"/>
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B94,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B94,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D94" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B94,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B94,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -2440,11 +2440,11 @@
       <c r="A95" s="5" t="n"/>
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B95,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B95,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D95" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B95,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B95,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -2459,11 +2459,11 @@
       <c r="A96" s="5" t="n"/>
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B96,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B96,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D96" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B96,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B96,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -2478,11 +2478,11 @@
       <c r="A97" s="5" t="n"/>
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B97,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B97,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D97" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B97,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B97,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -2497,11 +2497,11 @@
       <c r="A98" s="5" t="n"/>
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B98,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B98,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D98" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B98,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B98,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -2516,11 +2516,11 @@
       <c r="A99" s="5" t="n"/>
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B99,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B99,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D99" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B99,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B99,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -2535,11 +2535,11 @@
       <c r="A100" s="5" t="n"/>
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B100,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B100,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D100" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B100,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B100,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E100" s="8" t="n"/>
@@ -2554,11 +2554,11 @@
       <c r="A101" s="5" t="n"/>
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B101,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B101,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D101" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B101,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B101,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -2573,11 +2573,11 @@
       <c r="A102" s="5" t="n"/>
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B102,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B102,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D102" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B102,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B102,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -2592,11 +2592,11 @@
       <c r="A103" s="5" t="n"/>
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B103,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B103,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D103" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B103,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B103,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -2611,11 +2611,11 @@
       <c r="A104" s="5" t="n"/>
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B104,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B104,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D104" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B104,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B104,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E104" s="8" t="n"/>
@@ -2630,11 +2630,11 @@
       <c r="A105" s="5" t="n"/>
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B105,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B105,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D105" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B105,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B105,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E105" s="8" t="n"/>
@@ -2649,11 +2649,11 @@
       <c r="A106" s="5" t="n"/>
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B106,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B106,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D106" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B106,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B106,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E106" s="8" t="n"/>
@@ -2668,11 +2668,11 @@
       <c r="A107" s="5" t="n"/>
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B107,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B107,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D107" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B107,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B107,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E107" s="8" t="n"/>
@@ -2687,11 +2687,11 @@
       <c r="A108" s="5" t="n"/>
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B108,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B108,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D108" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B108,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B108,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E108" s="8" t="n"/>
@@ -2706,11 +2706,11 @@
       <c r="A109" s="5" t="n"/>
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B109,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B109,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D109" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B109,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B109,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E109" s="8" t="n"/>
@@ -2725,11 +2725,11 @@
       <c r="A110" s="5" t="n"/>
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B110,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B110,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D110" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B110,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B110,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E110" s="8" t="n"/>
@@ -2744,11 +2744,11 @@
       <c r="A111" s="5" t="n"/>
       <c r="B111" s="5" t="n"/>
       <c r="C111" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B111,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B111,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D111" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B111,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B111,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E111" s="8" t="n"/>
@@ -2763,11 +2763,11 @@
       <c r="A112" s="5" t="n"/>
       <c r="B112" s="5" t="n"/>
       <c r="C112" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B112,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B112,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D112" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B112,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B112,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E112" s="8" t="n"/>
@@ -2782,11 +2782,11 @@
       <c r="A113" s="5" t="n"/>
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B113,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B113,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D113" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B113,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B113,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E113" s="8" t="n"/>
@@ -2801,11 +2801,11 @@
       <c r="A114" s="5" t="n"/>
       <c r="B114" s="5" t="n"/>
       <c r="C114" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B114,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B114,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D114" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B114,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B114,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E114" s="8" t="n"/>
@@ -2820,11 +2820,11 @@
       <c r="A115" s="5" t="n"/>
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B115,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B115,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D115" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B115,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B115,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E115" s="8" t="n"/>
@@ -2839,11 +2839,11 @@
       <c r="A116" s="5" t="n"/>
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B116,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B116,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D116" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B116,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B116,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E116" s="8" t="n"/>
@@ -2858,11 +2858,11 @@
       <c r="A117" s="5" t="n"/>
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B117,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B117,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D117" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B117,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B117,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E117" s="8" t="n"/>
@@ -2877,11 +2877,11 @@
       <c r="A118" s="5" t="n"/>
       <c r="B118" s="5" t="n"/>
       <c r="C118" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B118,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B118,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D118" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B118,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B118,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E118" s="8" t="n"/>
@@ -2896,11 +2896,11 @@
       <c r="A119" s="5" t="n"/>
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B119,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B119,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D119" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B119,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B119,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E119" s="8" t="n"/>
@@ -2915,11 +2915,11 @@
       <c r="A120" s="5" t="n"/>
       <c r="B120" s="5" t="n"/>
       <c r="C120" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B120,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B120,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D120" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B120,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B120,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E120" s="8" t="n"/>
@@ -2934,11 +2934,11 @@
       <c r="A121" s="5" t="n"/>
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B121,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B121,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D121" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B121,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B121,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E121" s="8" t="n"/>
@@ -2953,11 +2953,11 @@
       <c r="A122" s="5" t="n"/>
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B122,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B122,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D122" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B122,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B122,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E122" s="8" t="n"/>
@@ -2972,11 +2972,11 @@
       <c r="A123" s="5" t="n"/>
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B123,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B123,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D123" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B123,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B123,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E123" s="8" t="n"/>
@@ -2991,11 +2991,11 @@
       <c r="A124" s="5" t="n"/>
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B124,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B124,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D124" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B124,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B124,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E124" s="8" t="n"/>
@@ -3010,11 +3010,11 @@
       <c r="A125" s="5" t="n"/>
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B125,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B125,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D125" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B125,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B125,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E125" s="8" t="n"/>
@@ -3029,11 +3029,11 @@
       <c r="A126" s="5" t="n"/>
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B126,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B126,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D126" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B126,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B126,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E126" s="8" t="n"/>
@@ -3048,11 +3048,11 @@
       <c r="A127" s="5" t="n"/>
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B127,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B127,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D127" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B127,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B127,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E127" s="8" t="n"/>
@@ -3067,11 +3067,11 @@
       <c r="A128" s="5" t="n"/>
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B128,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B128,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D128" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B128,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B128,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E128" s="8" t="n"/>
@@ -3086,11 +3086,11 @@
       <c r="A129" s="5" t="n"/>
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B129,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B129,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D129" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B129,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B129,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E129" s="8" t="n"/>
@@ -3105,11 +3105,11 @@
       <c r="A130" s="5" t="n"/>
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B130,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B130,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D130" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B130,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B130,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E130" s="8" t="n"/>
@@ -3124,11 +3124,11 @@
       <c r="A131" s="5" t="n"/>
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B131,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B131,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D131" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B131,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B131,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E131" s="8" t="n"/>
@@ -3143,11 +3143,11 @@
       <c r="A132" s="5" t="n"/>
       <c r="B132" s="5" t="n"/>
       <c r="C132" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B132,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B132,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D132" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B132,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B132,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E132" s="8" t="n"/>
@@ -3162,11 +3162,11 @@
       <c r="A133" s="5" t="n"/>
       <c r="B133" s="5" t="n"/>
       <c r="C133" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B133,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B133,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D133" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B133,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B133,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E133" s="8" t="n"/>
@@ -3181,11 +3181,11 @@
       <c r="A134" s="5" t="n"/>
       <c r="B134" s="5" t="n"/>
       <c r="C134" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B134,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B134,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D134" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B134,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B134,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E134" s="8" t="n"/>
@@ -3200,11 +3200,11 @@
       <c r="A135" s="5" t="n"/>
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B135,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B135,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D135" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B135,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B135,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E135" s="8" t="n"/>
@@ -3219,11 +3219,11 @@
       <c r="A136" s="5" t="n"/>
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B136,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B136,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D136" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B136,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B136,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E136" s="8" t="n"/>
@@ -3238,11 +3238,11 @@
       <c r="A137" s="5" t="n"/>
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B137,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B137,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D137" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B137,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B137,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E137" s="8" t="n"/>
@@ -3257,11 +3257,11 @@
       <c r="A138" s="5" t="n"/>
       <c r="B138" s="5" t="n"/>
       <c r="C138" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B138,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B138,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D138" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B138,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B138,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E138" s="8" t="n"/>
@@ -3276,11 +3276,11 @@
       <c r="A139" s="5" t="n"/>
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B139,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B139,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D139" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B139,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B139,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E139" s="8" t="n"/>
@@ -3295,11 +3295,11 @@
       <c r="A140" s="5" t="n"/>
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B140,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B140,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D140" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B140,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B140,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E140" s="8" t="n"/>
@@ -3314,11 +3314,11 @@
       <c r="A141" s="5" t="n"/>
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B141,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B141,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D141" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B141,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B141,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E141" s="8" t="n"/>
@@ -3333,11 +3333,11 @@
       <c r="A142" s="5" t="n"/>
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B142,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B142,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D142" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B142,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B142,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E142" s="8" t="n"/>
@@ -3352,11 +3352,11 @@
       <c r="A143" s="5" t="n"/>
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B143,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B143,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D143" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B143,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B143,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E143" s="8" t="n"/>
@@ -3371,11 +3371,11 @@
       <c r="A144" s="5" t="n"/>
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B144,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B144,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D144" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B144,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B144,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E144" s="8" t="n"/>
@@ -3390,11 +3390,11 @@
       <c r="A145" s="5" t="n"/>
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B145,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B145,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D145" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B145,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B145,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E145" s="8" t="n"/>
@@ -3409,11 +3409,11 @@
       <c r="A146" s="5" t="n"/>
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B146,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B146,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D146" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B146,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B146,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E146" s="8" t="n"/>
@@ -3428,11 +3428,11 @@
       <c r="A147" s="5" t="n"/>
       <c r="B147" s="5" t="n"/>
       <c r="C147" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B147,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B147,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D147" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B147,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B147,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E147" s="8" t="n"/>
@@ -3447,11 +3447,11 @@
       <c r="A148" s="5" t="n"/>
       <c r="B148" s="5" t="n"/>
       <c r="C148" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B148,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B148,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D148" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B148,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B148,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E148" s="8" t="n"/>
@@ -3466,11 +3466,11 @@
       <c r="A149" s="5" t="n"/>
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B149,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B149,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D149" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B149,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B149,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E149" s="8" t="n"/>
@@ -3485,11 +3485,11 @@
       <c r="A150" s="5" t="n"/>
       <c r="B150" s="5" t="n"/>
       <c r="C150" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B150,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B150,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D150" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B150,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B150,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E150" s="8" t="n"/>
@@ -3504,11 +3504,11 @@
       <c r="A151" s="5" t="n"/>
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B151,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B151,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D151" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B151,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B151,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E151" s="8" t="n"/>
@@ -3523,11 +3523,11 @@
       <c r="A152" s="5" t="n"/>
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B152,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B152,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D152" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B152,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B152,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E152" s="8" t="n"/>
@@ -3542,11 +3542,11 @@
       <c r="A153" s="5" t="n"/>
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B153,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B153,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D153" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B153,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B153,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E153" s="8" t="n"/>
@@ -3561,11 +3561,11 @@
       <c r="A154" s="5" t="n"/>
       <c r="B154" s="5" t="n"/>
       <c r="C154" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B154,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B154,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D154" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B154,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B154,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E154" s="8" t="n"/>
@@ -3580,11 +3580,11 @@
       <c r="A155" s="5" t="n"/>
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B155,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B155,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D155" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B155,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B155,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E155" s="8" t="n"/>
@@ -3599,11 +3599,11 @@
       <c r="A156" s="5" t="n"/>
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B156,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B156,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D156" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B156,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B156,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E156" s="8" t="n"/>
@@ -3618,11 +3618,11 @@
       <c r="A157" s="5" t="n"/>
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B157,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B157,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D157" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B157,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B157,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E157" s="8" t="n"/>
@@ -3637,11 +3637,11 @@
       <c r="A158" s="5" t="n"/>
       <c r="B158" s="5" t="n"/>
       <c r="C158" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B158,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B158,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D158" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B158,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B158,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E158" s="8" t="n"/>
@@ -3656,11 +3656,11 @@
       <c r="A159" s="5" t="n"/>
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B159,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B159,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D159" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B159,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B159,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E159" s="8" t="n"/>
@@ -3675,11 +3675,11 @@
       <c r="A160" s="5" t="n"/>
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B160,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B160,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D160" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B160,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B160,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E160" s="8" t="n"/>
@@ -3694,11 +3694,11 @@
       <c r="A161" s="5" t="n"/>
       <c r="B161" s="5" t="n"/>
       <c r="C161" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B161,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B161,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D161" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B161,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B161,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E161" s="8" t="n"/>
@@ -3713,11 +3713,11 @@
       <c r="A162" s="5" t="n"/>
       <c r="B162" s="5" t="n"/>
       <c r="C162" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B162,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B162,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D162" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B162,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B162,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E162" s="8" t="n"/>
@@ -3732,11 +3732,11 @@
       <c r="A163" s="5" t="n"/>
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B163,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B163,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D163" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B163,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B163,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E163" s="8" t="n"/>
@@ -3751,11 +3751,11 @@
       <c r="A164" s="5" t="n"/>
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B164,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B164,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D164" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B164,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B164,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E164" s="8" t="n"/>
@@ -3770,11 +3770,11 @@
       <c r="A165" s="5" t="n"/>
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B165,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B165,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D165" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B165,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B165,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E165" s="8" t="n"/>
@@ -3789,11 +3789,11 @@
       <c r="A166" s="5" t="n"/>
       <c r="B166" s="5" t="n"/>
       <c r="C166" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B166,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B166,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D166" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B166,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B166,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E166" s="8" t="n"/>
@@ -3808,11 +3808,11 @@
       <c r="A167" s="5" t="n"/>
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B167,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B167,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D167" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B167,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B167,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E167" s="8" t="n"/>
@@ -3827,11 +3827,11 @@
       <c r="A168" s="5" t="n"/>
       <c r="B168" s="5" t="n"/>
       <c r="C168" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B168,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B168,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D168" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B168,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B168,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E168" s="8" t="n"/>
@@ -3846,11 +3846,11 @@
       <c r="A169" s="5" t="n"/>
       <c r="B169" s="5" t="n"/>
       <c r="C169" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B169,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B169,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D169" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B169,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B169,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E169" s="8" t="n"/>
@@ -3865,11 +3865,11 @@
       <c r="A170" s="5" t="n"/>
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B170,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B170,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D170" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B170,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B170,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E170" s="8" t="n"/>
@@ -3884,11 +3884,11 @@
       <c r="A171" s="5" t="n"/>
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B171,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B171,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D171" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B171,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B171,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E171" s="8" t="n"/>
@@ -3903,11 +3903,11 @@
       <c r="A172" s="5" t="n"/>
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B172,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B172,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D172" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B172,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B172,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E172" s="8" t="n"/>
@@ -3922,11 +3922,11 @@
       <c r="A173" s="5" t="n"/>
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B173,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B173,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D173" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B173,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B173,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E173" s="8" t="n"/>
@@ -3941,11 +3941,11 @@
       <c r="A174" s="5" t="n"/>
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B174,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B174,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D174" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B174,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B174,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E174" s="8" t="n"/>
@@ -3960,11 +3960,11 @@
       <c r="A175" s="5" t="n"/>
       <c r="B175" s="5" t="n"/>
       <c r="C175" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B175,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B175,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D175" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B175,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B175,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E175" s="8" t="n"/>
@@ -3979,11 +3979,11 @@
       <c r="A176" s="5" t="n"/>
       <c r="B176" s="5" t="n"/>
       <c r="C176" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B176,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B176,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D176" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B176,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B176,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E176" s="8" t="n"/>
@@ -3998,11 +3998,11 @@
       <c r="A177" s="5" t="n"/>
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B177,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B177,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D177" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B177,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B177,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E177" s="8" t="n"/>
@@ -4017,11 +4017,11 @@
       <c r="A178" s="5" t="n"/>
       <c r="B178" s="5" t="n"/>
       <c r="C178" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B178,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B178,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D178" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B178,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B178,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E178" s="8" t="n"/>
@@ -4036,11 +4036,11 @@
       <c r="A179" s="5" t="n"/>
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B179,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B179,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D179" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B179,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B179,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E179" s="8" t="n"/>
@@ -4055,11 +4055,11 @@
       <c r="A180" s="5" t="n"/>
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B180,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B180,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D180" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B180,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B180,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E180" s="8" t="n"/>
@@ -4074,11 +4074,11 @@
       <c r="A181" s="5" t="n"/>
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B181,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B181,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D181" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B181,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B181,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E181" s="8" t="n"/>
@@ -4093,11 +4093,11 @@
       <c r="A182" s="5" t="n"/>
       <c r="B182" s="5" t="n"/>
       <c r="C182" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B182,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B182,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D182" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B182,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B182,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E182" s="8" t="n"/>
@@ -4112,11 +4112,11 @@
       <c r="A183" s="5" t="n"/>
       <c r="B183" s="5" t="n"/>
       <c r="C183" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B183,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B183,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D183" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B183,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B183,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E183" s="8" t="n"/>
@@ -4131,11 +4131,11 @@
       <c r="A184" s="5" t="n"/>
       <c r="B184" s="5" t="n"/>
       <c r="C184" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B184,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B184,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D184" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B184,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B184,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E184" s="8" t="n"/>
@@ -4150,11 +4150,11 @@
       <c r="A185" s="5" t="n"/>
       <c r="B185" s="5" t="n"/>
       <c r="C185" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B185,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B185,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D185" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B185,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B185,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E185" s="8" t="n"/>
@@ -4169,11 +4169,11 @@
       <c r="A186" s="5" t="n"/>
       <c r="B186" s="5" t="n"/>
       <c r="C186" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B186,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B186,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D186" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B186,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B186,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E186" s="8" t="n"/>
@@ -4188,11 +4188,11 @@
       <c r="A187" s="5" t="n"/>
       <c r="B187" s="5" t="n"/>
       <c r="C187" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B187,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B187,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D187" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B187,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B187,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E187" s="8" t="n"/>
@@ -4207,11 +4207,11 @@
       <c r="A188" s="5" t="n"/>
       <c r="B188" s="5" t="n"/>
       <c r="C188" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B188,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B188,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D188" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B188,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B188,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E188" s="8" t="n"/>
@@ -4226,11 +4226,11 @@
       <c r="A189" s="5" t="n"/>
       <c r="B189" s="5" t="n"/>
       <c r="C189" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B189,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B189,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D189" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B189,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B189,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E189" s="8" t="n"/>
@@ -4245,11 +4245,11 @@
       <c r="A190" s="5" t="n"/>
       <c r="B190" s="5" t="n"/>
       <c r="C190" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B190,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B190,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D190" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B190,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B190,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E190" s="8" t="n"/>
@@ -4264,11 +4264,11 @@
       <c r="A191" s="5" t="n"/>
       <c r="B191" s="5" t="n"/>
       <c r="C191" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B191,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B191,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D191" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B191,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B191,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E191" s="8" t="n"/>
@@ -4283,11 +4283,11 @@
       <c r="A192" s="5" t="n"/>
       <c r="B192" s="5" t="n"/>
       <c r="C192" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B192,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B192,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D192" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B192,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B192,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E192" s="8" t="n"/>
@@ -4302,11 +4302,11 @@
       <c r="A193" s="5" t="n"/>
       <c r="B193" s="5" t="n"/>
       <c r="C193" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B193,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B193,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D193" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B193,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B193,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E193" s="8" t="n"/>
@@ -4321,11 +4321,11 @@
       <c r="A194" s="5" t="n"/>
       <c r="B194" s="5" t="n"/>
       <c r="C194" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B194,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B194,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D194" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B194,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B194,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E194" s="8" t="n"/>
@@ -4340,11 +4340,11 @@
       <c r="A195" s="5" t="n"/>
       <c r="B195" s="5" t="n"/>
       <c r="C195" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B195,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B195,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D195" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B195,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B195,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E195" s="8" t="n"/>
@@ -4359,11 +4359,11 @@
       <c r="A196" s="5" t="n"/>
       <c r="B196" s="5" t="n"/>
       <c r="C196" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B196,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B196,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D196" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B196,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B196,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E196" s="8" t="n"/>
@@ -4378,11 +4378,11 @@
       <c r="A197" s="5" t="n"/>
       <c r="B197" s="5" t="n"/>
       <c r="C197" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B197,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B197,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D197" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B197,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B197,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E197" s="8" t="n"/>
@@ -4397,11 +4397,11 @@
       <c r="A198" s="5" t="n"/>
       <c r="B198" s="5" t="n"/>
       <c r="C198" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B198,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B198,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D198" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B198,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B198,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E198" s="8" t="n"/>
@@ -4416,11 +4416,11 @@
       <c r="A199" s="5" t="n"/>
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B199,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B199,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D199" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B199,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B199,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E199" s="8" t="n"/>
@@ -4435,11 +4435,11 @@
       <c r="A200" s="5" t="n"/>
       <c r="B200" s="5" t="n"/>
       <c r="C200" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B200,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B200,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D200" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B200,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B200,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E200" s="8" t="n"/>
@@ -4454,11 +4454,11 @@
       <c r="A201" s="5" t="n"/>
       <c r="B201" s="5" t="n"/>
       <c r="C201" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B201,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B201,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D201" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B201,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B201,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E201" s="8" t="n"/>
@@ -4473,11 +4473,11 @@
       <c r="A202" s="5" t="n"/>
       <c r="B202" s="5" t="n"/>
       <c r="C202" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B202,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B202,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D202" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B202,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B202,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E202" s="8" t="n"/>
@@ -4492,11 +4492,11 @@
       <c r="A203" s="5" t="n"/>
       <c r="B203" s="5" t="n"/>
       <c r="C203" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B203,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B203,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D203" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B203,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B203,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E203" s="8" t="n"/>
@@ -4511,11 +4511,11 @@
       <c r="A204" s="5" t="n"/>
       <c r="B204" s="5" t="n"/>
       <c r="C204" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B204,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B204,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D204" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B204,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B204,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E204" s="8" t="n"/>
@@ -4530,11 +4530,11 @@
       <c r="A205" s="5" t="n"/>
       <c r="B205" s="5" t="n"/>
       <c r="C205" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B205,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B205,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D205" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B205,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B205,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E205" s="8" t="n"/>
@@ -4549,11 +4549,11 @@
       <c r="A206" s="5" t="n"/>
       <c r="B206" s="5" t="n"/>
       <c r="C206" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B206,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B206,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D206" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B206,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B206,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E206" s="8" t="n"/>
@@ -4568,11 +4568,11 @@
       <c r="A207" s="5" t="n"/>
       <c r="B207" s="5" t="n"/>
       <c r="C207" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B207,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B207,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D207" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B207,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B207,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E207" s="8" t="n"/>
@@ -4587,11 +4587,11 @@
       <c r="A208" s="5" t="n"/>
       <c r="B208" s="5" t="n"/>
       <c r="C208" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B208,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B208,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D208" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B208,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B208,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E208" s="8" t="n"/>
@@ -4606,11 +4606,11 @@
       <c r="A209" s="5" t="n"/>
       <c r="B209" s="5" t="n"/>
       <c r="C209" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B209,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B209,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D209" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B209,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B209,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E209" s="8" t="n"/>
@@ -4625,11 +4625,11 @@
       <c r="A210" s="5" t="n"/>
       <c r="B210" s="5" t="n"/>
       <c r="C210" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B210,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B210,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D210" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B210,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B210,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E210" s="8" t="n"/>
@@ -4644,11 +4644,11 @@
       <c r="A211" s="5" t="n"/>
       <c r="B211" s="5" t="n"/>
       <c r="C211" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B211,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B211,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D211" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B211,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B211,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E211" s="8" t="n"/>
@@ -4663,11 +4663,11 @@
       <c r="A212" s="5" t="n"/>
       <c r="B212" s="5" t="n"/>
       <c r="C212" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B212,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B212,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D212" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B212,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B212,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E212" s="8" t="n"/>
@@ -4682,11 +4682,11 @@
       <c r="A213" s="5" t="n"/>
       <c r="B213" s="5" t="n"/>
       <c r="C213" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B213,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B213,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D213" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B213,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B213,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E213" s="8" t="n"/>
@@ -4701,11 +4701,11 @@
       <c r="A214" s="5" t="n"/>
       <c r="B214" s="5" t="n"/>
       <c r="C214" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B214,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B214,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D214" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B214,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B214,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E214" s="8" t="n"/>
@@ -4720,11 +4720,11 @@
       <c r="A215" s="5" t="n"/>
       <c r="B215" s="5" t="n"/>
       <c r="C215" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B215,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B215,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D215" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B215,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B215,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E215" s="8" t="n"/>
@@ -4739,11 +4739,11 @@
       <c r="A216" s="5" t="n"/>
       <c r="B216" s="5" t="n"/>
       <c r="C216" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B216,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B216,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D216" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B216,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B216,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E216" s="8" t="n"/>
@@ -4758,11 +4758,11 @@
       <c r="A217" s="5" t="n"/>
       <c r="B217" s="5" t="n"/>
       <c r="C217" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B217,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B217,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D217" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B217,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B217,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E217" s="8" t="n"/>
@@ -4777,11 +4777,11 @@
       <c r="A218" s="5" t="n"/>
       <c r="B218" s="5" t="n"/>
       <c r="C218" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B218,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B218,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D218" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B218,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B218,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E218" s="8" t="n"/>
@@ -4796,11 +4796,11 @@
       <c r="A219" s="5" t="n"/>
       <c r="B219" s="5" t="n"/>
       <c r="C219" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B219,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B219,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D219" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B219,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B219,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E219" s="8" t="n"/>
@@ -4815,11 +4815,11 @@
       <c r="A220" s="5" t="n"/>
       <c r="B220" s="5" t="n"/>
       <c r="C220" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B220,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B220,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D220" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B220,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B220,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E220" s="8" t="n"/>
@@ -4834,11 +4834,11 @@
       <c r="A221" s="5" t="n"/>
       <c r="B221" s="5" t="n"/>
       <c r="C221" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B221,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B221,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D221" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B221,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B221,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E221" s="8" t="n"/>
@@ -4853,11 +4853,11 @@
       <c r="A222" s="5" t="n"/>
       <c r="B222" s="5" t="n"/>
       <c r="C222" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B222,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B222,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D222" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B222,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B222,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E222" s="8" t="n"/>
@@ -4872,11 +4872,11 @@
       <c r="A223" s="5" t="n"/>
       <c r="B223" s="5" t="n"/>
       <c r="C223" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B223,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B223,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D223" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B223,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B223,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E223" s="8" t="n"/>
@@ -4891,11 +4891,11 @@
       <c r="A224" s="5" t="n"/>
       <c r="B224" s="5" t="n"/>
       <c r="C224" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B224,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B224,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D224" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B224,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B224,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E224" s="8" t="n"/>
@@ -4910,11 +4910,11 @@
       <c r="A225" s="5" t="n"/>
       <c r="B225" s="5" t="n"/>
       <c r="C225" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B225,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B225,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D225" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B225,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B225,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E225" s="8" t="n"/>
@@ -4929,11 +4929,11 @@
       <c r="A226" s="5" t="n"/>
       <c r="B226" s="5" t="n"/>
       <c r="C226" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B226,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B226,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D226" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B226,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B226,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E226" s="8" t="n"/>
@@ -4948,11 +4948,11 @@
       <c r="A227" s="5" t="n"/>
       <c r="B227" s="5" t="n"/>
       <c r="C227" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B227,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B227,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D227" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B227,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B227,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E227" s="8" t="n"/>
@@ -4967,11 +4967,11 @@
       <c r="A228" s="5" t="n"/>
       <c r="B228" s="5" t="n"/>
       <c r="C228" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B228,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B228,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D228" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B228,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B228,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E228" s="8" t="n"/>
@@ -4986,11 +4986,11 @@
       <c r="A229" s="5" t="n"/>
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B229,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B229,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D229" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B229,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B229,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E229" s="8" t="n"/>
@@ -5005,11 +5005,11 @@
       <c r="A230" s="5" t="n"/>
       <c r="B230" s="5" t="n"/>
       <c r="C230" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B230,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B230,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D230" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B230,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B230,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E230" s="8" t="n"/>
@@ -5024,11 +5024,11 @@
       <c r="A231" s="5" t="n"/>
       <c r="B231" s="5" t="n"/>
       <c r="C231" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B231,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B231,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D231" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B231,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B231,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E231" s="8" t="n"/>
@@ -5043,11 +5043,11 @@
       <c r="A232" s="5" t="n"/>
       <c r="B232" s="5" t="n"/>
       <c r="C232" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B232,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B232,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D232" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B232,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B232,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E232" s="8" t="n"/>
@@ -5062,11 +5062,11 @@
       <c r="A233" s="5" t="n"/>
       <c r="B233" s="5" t="n"/>
       <c r="C233" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B233,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B233,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D233" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B233,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B233,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E233" s="8" t="n"/>
@@ -5081,11 +5081,11 @@
       <c r="A234" s="5" t="n"/>
       <c r="B234" s="5" t="n"/>
       <c r="C234" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B234,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B234,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D234" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B234,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B234,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E234" s="8" t="n"/>
@@ -5100,11 +5100,11 @@
       <c r="A235" s="5" t="n"/>
       <c r="B235" s="5" t="n"/>
       <c r="C235" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B235,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B235,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D235" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B235,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B235,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E235" s="8" t="n"/>
@@ -5119,11 +5119,11 @@
       <c r="A236" s="5" t="n"/>
       <c r="B236" s="5" t="n"/>
       <c r="C236" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B236,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B236,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D236" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B236,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B236,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E236" s="8" t="n"/>
@@ -5138,11 +5138,11 @@
       <c r="A237" s="5" t="n"/>
       <c r="B237" s="5" t="n"/>
       <c r="C237" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B237,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B237,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D237" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B237,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B237,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E237" s="8" t="n"/>
@@ -5157,11 +5157,11 @@
       <c r="A238" s="5" t="n"/>
       <c r="B238" s="5" t="n"/>
       <c r="C238" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B238,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B238,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D238" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B238,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B238,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E238" s="8" t="n"/>
@@ -5176,11 +5176,11 @@
       <c r="A239" s="5" t="n"/>
       <c r="B239" s="5" t="n"/>
       <c r="C239" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B239,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B239,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D239" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B239,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B239,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E239" s="8" t="n"/>
@@ -5195,11 +5195,11 @@
       <c r="A240" s="5" t="n"/>
       <c r="B240" s="5" t="n"/>
       <c r="C240" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B240,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B240,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D240" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B240,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B240,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E240" s="8" t="n"/>
@@ -5214,11 +5214,11 @@
       <c r="A241" s="5" t="n"/>
       <c r="B241" s="5" t="n"/>
       <c r="C241" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B241,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B241,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D241" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B241,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B241,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E241" s="8" t="n"/>
@@ -5233,11 +5233,11 @@
       <c r="A242" s="5" t="n"/>
       <c r="B242" s="5" t="n"/>
       <c r="C242" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B242,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B242,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D242" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B242,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B242,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E242" s="8" t="n"/>
@@ -5252,11 +5252,11 @@
       <c r="A243" s="5" t="n"/>
       <c r="B243" s="5" t="n"/>
       <c r="C243" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B243,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B243,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D243" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B243,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B243,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E243" s="8" t="n"/>
@@ -5271,11 +5271,11 @@
       <c r="A244" s="5" t="n"/>
       <c r="B244" s="5" t="n"/>
       <c r="C244" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B244,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B244,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D244" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B244,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B244,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E244" s="8" t="n"/>
@@ -5290,11 +5290,11 @@
       <c r="A245" s="5" t="n"/>
       <c r="B245" s="5" t="n"/>
       <c r="C245" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B245,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B245,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D245" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B245,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B245,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E245" s="8" t="n"/>
@@ -5309,11 +5309,11 @@
       <c r="A246" s="5" t="n"/>
       <c r="B246" s="5" t="n"/>
       <c r="C246" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B246,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B246,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D246" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B246,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B246,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E246" s="8" t="n"/>
@@ -5328,11 +5328,11 @@
       <c r="A247" s="5" t="n"/>
       <c r="B247" s="5" t="n"/>
       <c r="C247" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B247,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B247,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D247" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B247,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B247,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E247" s="8" t="n"/>
@@ -5347,11 +5347,11 @@
       <c r="A248" s="5" t="n"/>
       <c r="B248" s="5" t="n"/>
       <c r="C248" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B248,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B248,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D248" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B248,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B248,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E248" s="8" t="n"/>
@@ -5366,11 +5366,11 @@
       <c r="A249" s="5" t="n"/>
       <c r="B249" s="5" t="n"/>
       <c r="C249" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B249,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B249,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D249" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B249,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B249,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E249" s="8" t="n"/>
@@ -5385,11 +5385,11 @@
       <c r="A250" s="5" t="n"/>
       <c r="B250" s="5" t="n"/>
       <c r="C250" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B250,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B250,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D250" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B250,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B250,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E250" s="8" t="n"/>
@@ -5404,11 +5404,11 @@
       <c r="A251" s="5" t="n"/>
       <c r="B251" s="5" t="n"/>
       <c r="C251" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B251,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B251,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D251" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B251,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B251,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E251" s="8" t="n"/>
@@ -5423,11 +5423,11 @@
       <c r="A252" s="5" t="n"/>
       <c r="B252" s="5" t="n"/>
       <c r="C252" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B252,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B252,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D252" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B252,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B252,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E252" s="8" t="n"/>
@@ -5442,11 +5442,11 @@
       <c r="A253" s="5" t="n"/>
       <c r="B253" s="5" t="n"/>
       <c r="C253" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B253,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B253,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D253" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B253,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B253,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E253" s="8" t="n"/>
@@ -5461,11 +5461,11 @@
       <c r="A254" s="5" t="n"/>
       <c r="B254" s="5" t="n"/>
       <c r="C254" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B254,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B254,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D254" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B254,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B254,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E254" s="8" t="n"/>
@@ -5480,11 +5480,11 @@
       <c r="A255" s="5" t="n"/>
       <c r="B255" s="5" t="n"/>
       <c r="C255" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B255,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B255,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D255" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B255,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B255,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E255" s="8" t="n"/>
@@ -5499,11 +5499,11 @@
       <c r="A256" s="5" t="n"/>
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B256,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B256,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D256" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B256,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B256,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E256" s="8" t="n"/>
@@ -5518,11 +5518,11 @@
       <c r="A257" s="5" t="n"/>
       <c r="B257" s="5" t="n"/>
       <c r="C257" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B257,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B257,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D257" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B257,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B257,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E257" s="8" t="n"/>
@@ -5537,11 +5537,11 @@
       <c r="A258" s="5" t="n"/>
       <c r="B258" s="5" t="n"/>
       <c r="C258" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B258,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B258,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D258" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B258,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B258,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E258" s="8" t="n"/>
@@ -5556,11 +5556,11 @@
       <c r="A259" s="5" t="n"/>
       <c r="B259" s="5" t="n"/>
       <c r="C259" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B259,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B259,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D259" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B259,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B259,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E259" s="8" t="n"/>
@@ -5575,11 +5575,11 @@
       <c r="A260" s="5" t="n"/>
       <c r="B260" s="5" t="n"/>
       <c r="C260" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B260,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B260,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D260" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B260,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B260,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E260" s="8" t="n"/>
@@ -5594,11 +5594,11 @@
       <c r="A261" s="5" t="n"/>
       <c r="B261" s="5" t="n"/>
       <c r="C261" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B261,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B261,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D261" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B261,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B261,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E261" s="8" t="n"/>
@@ -5613,11 +5613,11 @@
       <c r="A262" s="5" t="n"/>
       <c r="B262" s="5" t="n"/>
       <c r="C262" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B262,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B262,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D262" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B262,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B262,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E262" s="8" t="n"/>
@@ -5632,11 +5632,11 @@
       <c r="A263" s="5" t="n"/>
       <c r="B263" s="5" t="n"/>
       <c r="C263" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B263,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B263,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D263" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B263,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B263,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E263" s="8" t="n"/>
@@ -5651,11 +5651,11 @@
       <c r="A264" s="5" t="n"/>
       <c r="B264" s="5" t="n"/>
       <c r="C264" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B264,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B264,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D264" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B264,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B264,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E264" s="8" t="n"/>
@@ -5670,11 +5670,11 @@
       <c r="A265" s="5" t="n"/>
       <c r="B265" s="5" t="n"/>
       <c r="C265" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B265,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B265,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D265" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B265,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B265,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E265" s="8" t="n"/>
@@ -5689,11 +5689,11 @@
       <c r="A266" s="5" t="n"/>
       <c r="B266" s="5" t="n"/>
       <c r="C266" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B266,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B266,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D266" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B266,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B266,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E266" s="8" t="n"/>
@@ -5708,11 +5708,11 @@
       <c r="A267" s="5" t="n"/>
       <c r="B267" s="5" t="n"/>
       <c r="C267" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B267,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B267,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D267" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B267,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B267,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E267" s="8" t="n"/>
@@ -5727,11 +5727,11 @@
       <c r="A268" s="5" t="n"/>
       <c r="B268" s="5" t="n"/>
       <c r="C268" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B268,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B268,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D268" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B268,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B268,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E268" s="8" t="n"/>
@@ -5746,11 +5746,11 @@
       <c r="A269" s="5" t="n"/>
       <c r="B269" s="5" t="n"/>
       <c r="C269" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B269,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B269,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D269" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B269,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B269,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E269" s="8" t="n"/>
@@ -5765,11 +5765,11 @@
       <c r="A270" s="5" t="n"/>
       <c r="B270" s="5" t="n"/>
       <c r="C270" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B270,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B270,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D270" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B270,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B270,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E270" s="8" t="n"/>
@@ -5784,11 +5784,11 @@
       <c r="A271" s="5" t="n"/>
       <c r="B271" s="5" t="n"/>
       <c r="C271" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B271,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B271,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D271" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B271,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B271,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E271" s="8" t="n"/>
@@ -5803,11 +5803,11 @@
       <c r="A272" s="5" t="n"/>
       <c r="B272" s="5" t="n"/>
       <c r="C272" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B272,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B272,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D272" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B272,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B272,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E272" s="8" t="n"/>
@@ -5822,11 +5822,11 @@
       <c r="A273" s="5" t="n"/>
       <c r="B273" s="5" t="n"/>
       <c r="C273" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B273,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B273,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D273" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B273,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B273,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E273" s="8" t="n"/>
@@ -5841,11 +5841,11 @@
       <c r="A274" s="5" t="n"/>
       <c r="B274" s="5" t="n"/>
       <c r="C274" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B274,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B274,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D274" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B274,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B274,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E274" s="8" t="n"/>
@@ -5860,11 +5860,11 @@
       <c r="A275" s="5" t="n"/>
       <c r="B275" s="5" t="n"/>
       <c r="C275" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B275,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B275,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D275" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B275,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B275,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E275" s="8" t="n"/>
@@ -5879,11 +5879,11 @@
       <c r="A276" s="5" t="n"/>
       <c r="B276" s="5" t="n"/>
       <c r="C276" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B276,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B276,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D276" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B276,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B276,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E276" s="8" t="n"/>
@@ -5898,11 +5898,11 @@
       <c r="A277" s="5" t="n"/>
       <c r="B277" s="5" t="n"/>
       <c r="C277" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B277,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B277,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D277" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B277,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B277,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E277" s="8" t="n"/>
@@ -5917,11 +5917,11 @@
       <c r="A278" s="5" t="n"/>
       <c r="B278" s="5" t="n"/>
       <c r="C278" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B278,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B278,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D278" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B278,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B278,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E278" s="8" t="n"/>
@@ -5936,11 +5936,11 @@
       <c r="A279" s="5" t="n"/>
       <c r="B279" s="5" t="n"/>
       <c r="C279" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B279,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B279,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D279" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B279,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B279,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E279" s="8" t="n"/>
@@ -5955,11 +5955,11 @@
       <c r="A280" s="5" t="n"/>
       <c r="B280" s="5" t="n"/>
       <c r="C280" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B280,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B280,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D280" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B280,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B280,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E280" s="8" t="n"/>
@@ -5974,11 +5974,11 @@
       <c r="A281" s="5" t="n"/>
       <c r="B281" s="5" t="n"/>
       <c r="C281" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B281,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B281,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D281" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B281,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B281,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E281" s="8" t="n"/>
@@ -5993,11 +5993,11 @@
       <c r="A282" s="5" t="n"/>
       <c r="B282" s="5" t="n"/>
       <c r="C282" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B282,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B282,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D282" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B282,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B282,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E282" s="8" t="n"/>
@@ -6012,11 +6012,11 @@
       <c r="A283" s="5" t="n"/>
       <c r="B283" s="5" t="n"/>
       <c r="C283" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B283,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B283,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D283" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B283,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B283,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E283" s="8" t="n"/>
@@ -6031,11 +6031,11 @@
       <c r="A284" s="5" t="n"/>
       <c r="B284" s="5" t="n"/>
       <c r="C284" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B284,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B284,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D284" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B284,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B284,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E284" s="8" t="n"/>
@@ -6050,11 +6050,11 @@
       <c r="A285" s="5" t="n"/>
       <c r="B285" s="5" t="n"/>
       <c r="C285" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B285,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B285,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D285" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B285,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B285,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E285" s="8" t="n"/>
@@ -6069,11 +6069,11 @@
       <c r="A286" s="5" t="n"/>
       <c r="B286" s="5" t="n"/>
       <c r="C286" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B286,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B286,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D286" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B286,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B286,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E286" s="8" t="n"/>
@@ -6088,11 +6088,11 @@
       <c r="A287" s="5" t="n"/>
       <c r="B287" s="5" t="n"/>
       <c r="C287" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B287,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B287,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D287" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B287,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B287,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E287" s="8" t="n"/>
@@ -6107,11 +6107,11 @@
       <c r="A288" s="5" t="n"/>
       <c r="B288" s="5" t="n"/>
       <c r="C288" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B288,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B288,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D288" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B288,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B288,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E288" s="8" t="n"/>
@@ -6126,11 +6126,11 @@
       <c r="A289" s="5" t="n"/>
       <c r="B289" s="5" t="n"/>
       <c r="C289" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B289,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B289,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D289" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B289,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B289,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E289" s="8" t="n"/>
@@ -6145,11 +6145,11 @@
       <c r="A290" s="5" t="n"/>
       <c r="B290" s="5" t="n"/>
       <c r="C290" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B290,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B290,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D290" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B290,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B290,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E290" s="8" t="n"/>
@@ -6164,11 +6164,11 @@
       <c r="A291" s="5" t="n"/>
       <c r="B291" s="5" t="n"/>
       <c r="C291" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B291,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B291,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D291" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B291,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B291,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E291" s="8" t="n"/>
@@ -6183,11 +6183,11 @@
       <c r="A292" s="5" t="n"/>
       <c r="B292" s="5" t="n"/>
       <c r="C292" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B292,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B292,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D292" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B292,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B292,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E292" s="8" t="n"/>
@@ -6202,11 +6202,11 @@
       <c r="A293" s="5" t="n"/>
       <c r="B293" s="5" t="n"/>
       <c r="C293" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B293,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B293,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D293" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B293,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B293,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E293" s="8" t="n"/>
@@ -6221,11 +6221,11 @@
       <c r="A294" s="5" t="n"/>
       <c r="B294" s="5" t="n"/>
       <c r="C294" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B294,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B294,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D294" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B294,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B294,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E294" s="8" t="n"/>
@@ -6240,11 +6240,11 @@
       <c r="A295" s="5" t="n"/>
       <c r="B295" s="5" t="n"/>
       <c r="C295" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B295,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B295,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D295" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B295,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B295,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E295" s="8" t="n"/>
@@ -6259,11 +6259,11 @@
       <c r="A296" s="5" t="n"/>
       <c r="B296" s="5" t="n"/>
       <c r="C296" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B296,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B296,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D296" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B296,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B296,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E296" s="8" t="n"/>
@@ -6278,11 +6278,11 @@
       <c r="A297" s="5" t="n"/>
       <c r="B297" s="5" t="n"/>
       <c r="C297" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B297,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B297,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D297" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B297,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B297,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E297" s="8" t="n"/>
@@ -6297,11 +6297,11 @@
       <c r="A298" s="5" t="n"/>
       <c r="B298" s="5" t="n"/>
       <c r="C298" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B298,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B298,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D298" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B298,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B298,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E298" s="8" t="n"/>
@@ -6316,11 +6316,11 @@
       <c r="A299" s="5" t="n"/>
       <c r="B299" s="5" t="n"/>
       <c r="C299" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B299,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B299,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D299" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B299,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B299,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E299" s="8" t="n"/>
@@ -6335,11 +6335,11 @@
       <c r="A300" s="5" t="n"/>
       <c r="B300" s="5" t="n"/>
       <c r="C300" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B300,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B300,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D300" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B300,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B300,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E300" s="8" t="n"/>
@@ -6354,11 +6354,11 @@
       <c r="A301" s="5" t="n"/>
       <c r="B301" s="5" t="n"/>
       <c r="C301" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B301,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B301,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D301" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B301,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B301,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E301" s="8" t="n"/>
@@ -6373,11 +6373,11 @@
       <c r="A302" s="5" t="n"/>
       <c r="B302" s="5" t="n"/>
       <c r="C302" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B302,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B302,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D302" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B302,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B302,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E302" s="8" t="n"/>
@@ -6392,11 +6392,11 @@
       <c r="A303" s="5" t="n"/>
       <c r="B303" s="5" t="n"/>
       <c r="C303" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B303,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B303,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D303" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B303,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B303,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E303" s="8" t="n"/>
@@ -6411,11 +6411,11 @@
       <c r="A304" s="5" t="n"/>
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B304,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B304,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D304" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B304,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B304,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E304" s="8" t="n"/>
@@ -6430,11 +6430,11 @@
       <c r="A305" s="5" t="n"/>
       <c r="B305" s="5" t="n"/>
       <c r="C305" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B305,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B305,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D305" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B305,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B305,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E305" s="8" t="n"/>
@@ -6449,11 +6449,11 @@
       <c r="A306" s="5" t="n"/>
       <c r="B306" s="5" t="n"/>
       <c r="C306" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B306,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B306,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D306" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B306,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B306,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E306" s="8" t="n"/>
@@ -6468,11 +6468,11 @@
       <c r="A307" s="5" t="n"/>
       <c r="B307" s="5" t="n"/>
       <c r="C307" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B307,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B307,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D307" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B307,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B307,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E307" s="8" t="n"/>
@@ -6487,11 +6487,11 @@
       <c r="A308" s="5" t="n"/>
       <c r="B308" s="5" t="n"/>
       <c r="C308" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B308,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B308,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D308" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B308,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B308,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E308" s="8" t="n"/>
@@ -6506,11 +6506,11 @@
       <c r="A309" s="5" t="n"/>
       <c r="B309" s="5" t="n"/>
       <c r="C309" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B309,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B309,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D309" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B309,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B309,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E309" s="8" t="n"/>
@@ -6525,11 +6525,11 @@
       <c r="A310" s="5" t="n"/>
       <c r="B310" s="5" t="n"/>
       <c r="C310" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B310,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B310,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D310" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B310,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B310,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E310" s="8" t="n"/>
@@ -6544,11 +6544,11 @@
       <c r="A311" s="5" t="n"/>
       <c r="B311" s="5" t="n"/>
       <c r="C311" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B311,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B311,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D311" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B311,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B311,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E311" s="8" t="n"/>
@@ -6563,11 +6563,11 @@
       <c r="A312" s="5" t="n"/>
       <c r="B312" s="5" t="n"/>
       <c r="C312" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B312,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B312,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D312" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B312,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B312,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E312" s="8" t="n"/>
@@ -6582,11 +6582,11 @@
       <c r="A313" s="5" t="n"/>
       <c r="B313" s="5" t="n"/>
       <c r="C313" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B313,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B313,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D313" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B313,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B313,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E313" s="8" t="n"/>
@@ -6601,11 +6601,11 @@
       <c r="A314" s="5" t="n"/>
       <c r="B314" s="5" t="n"/>
       <c r="C314" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B314,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B314,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D314" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B314,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B314,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E314" s="8" t="n"/>
@@ -6620,11 +6620,11 @@
       <c r="A315" s="5" t="n"/>
       <c r="B315" s="5" t="n"/>
       <c r="C315" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B315,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B315,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D315" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B315,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B315,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E315" s="8" t="n"/>
@@ -6639,11 +6639,11 @@
       <c r="A316" s="5" t="n"/>
       <c r="B316" s="5" t="n"/>
       <c r="C316" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B316,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B316,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D316" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B316,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B316,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E316" s="8" t="n"/>
@@ -6658,11 +6658,11 @@
       <c r="A317" s="5" t="n"/>
       <c r="B317" s="5" t="n"/>
       <c r="C317" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B317,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B317,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D317" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B317,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B317,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E317" s="8" t="n"/>
@@ -6677,11 +6677,11 @@
       <c r="A318" s="5" t="n"/>
       <c r="B318" s="5" t="n"/>
       <c r="C318" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B318,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B318,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D318" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B318,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B318,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E318" s="8" t="n"/>
@@ -6696,11 +6696,11 @@
       <c r="A319" s="5" t="n"/>
       <c r="B319" s="5" t="n"/>
       <c r="C319" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B319,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B319,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D319" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B319,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B319,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E319" s="8" t="n"/>
@@ -6715,11 +6715,11 @@
       <c r="A320" s="5" t="n"/>
       <c r="B320" s="5" t="n"/>
       <c r="C320" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B320,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B320,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D320" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B320,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B320,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E320" s="8" t="n"/>
@@ -6734,11 +6734,11 @@
       <c r="A321" s="5" t="n"/>
       <c r="B321" s="5" t="n"/>
       <c r="C321" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B321,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B321,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D321" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B321,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B321,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E321" s="8" t="n"/>
@@ -6753,11 +6753,11 @@
       <c r="A322" s="5" t="n"/>
       <c r="B322" s="5" t="n"/>
       <c r="C322" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B322,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B322,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D322" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B322,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B322,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E322" s="8" t="n"/>
@@ -6772,11 +6772,11 @@
       <c r="A323" s="5" t="n"/>
       <c r="B323" s="5" t="n"/>
       <c r="C323" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B323,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B323,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D323" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B323,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B323,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E323" s="8" t="n"/>
@@ -6791,11 +6791,11 @@
       <c r="A324" s="5" t="n"/>
       <c r="B324" s="5" t="n"/>
       <c r="C324" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B324,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B324,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D324" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B324,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B324,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E324" s="8" t="n"/>
@@ -6810,11 +6810,11 @@
       <c r="A325" s="5" t="n"/>
       <c r="B325" s="5" t="n"/>
       <c r="C325" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B325,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B325,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D325" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B325,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B325,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E325" s="8" t="n"/>
@@ -6829,11 +6829,11 @@
       <c r="A326" s="5" t="n"/>
       <c r="B326" s="5" t="n"/>
       <c r="C326" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B326,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B326,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D326" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B326,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B326,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E326" s="8" t="n"/>
@@ -6848,11 +6848,11 @@
       <c r="A327" s="5" t="n"/>
       <c r="B327" s="5" t="n"/>
       <c r="C327" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B327,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B327,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D327" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B327,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B327,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E327" s="8" t="n"/>
@@ -6867,11 +6867,11 @@
       <c r="A328" s="5" t="n"/>
       <c r="B328" s="5" t="n"/>
       <c r="C328" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B328,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B328,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D328" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B328,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B328,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E328" s="8" t="n"/>
@@ -6886,11 +6886,11 @@
       <c r="A329" s="5" t="n"/>
       <c r="B329" s="5" t="n"/>
       <c r="C329" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B329,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B329,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D329" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B329,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B329,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E329" s="8" t="n"/>
@@ -6905,11 +6905,11 @@
       <c r="A330" s="5" t="n"/>
       <c r="B330" s="5" t="n"/>
       <c r="C330" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B330,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B330,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D330" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B330,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B330,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E330" s="8" t="n"/>
@@ -6924,11 +6924,11 @@
       <c r="A331" s="5" t="n"/>
       <c r="B331" s="5" t="n"/>
       <c r="C331" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B331,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B331,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D331" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B331,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B331,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E331" s="8" t="n"/>
@@ -6943,11 +6943,11 @@
       <c r="A332" s="5" t="n"/>
       <c r="B332" s="5" t="n"/>
       <c r="C332" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B332,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B332,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D332" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B332,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B332,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E332" s="8" t="n"/>
@@ -6962,11 +6962,11 @@
       <c r="A333" s="5" t="n"/>
       <c r="B333" s="5" t="n"/>
       <c r="C333" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B333,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B333,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D333" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B333,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B333,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E333" s="8" t="n"/>
@@ -6981,11 +6981,11 @@
       <c r="A334" s="5" t="n"/>
       <c r="B334" s="5" t="n"/>
       <c r="C334" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B334,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B334,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D334" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B334,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B334,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E334" s="8" t="n"/>
@@ -7000,11 +7000,11 @@
       <c r="A335" s="5" t="n"/>
       <c r="B335" s="5" t="n"/>
       <c r="C335" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B335,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B335,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D335" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B335,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B335,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E335" s="8" t="n"/>
@@ -7019,11 +7019,11 @@
       <c r="A336" s="5" t="n"/>
       <c r="B336" s="5" t="n"/>
       <c r="C336" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B336,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B336,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D336" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B336,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B336,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E336" s="8" t="n"/>
@@ -7038,11 +7038,11 @@
       <c r="A337" s="5" t="n"/>
       <c r="B337" s="5" t="n"/>
       <c r="C337" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B337,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B337,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D337" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B337,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B337,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E337" s="8" t="n"/>
@@ -7057,11 +7057,11 @@
       <c r="A338" s="5" t="n"/>
       <c r="B338" s="5" t="n"/>
       <c r="C338" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B338,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B338,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D338" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B338,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B338,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E338" s="8" t="n"/>
@@ -7076,11 +7076,11 @@
       <c r="A339" s="5" t="n"/>
       <c r="B339" s="5" t="n"/>
       <c r="C339" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B339,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B339,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D339" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B339,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B339,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E339" s="8" t="n"/>
@@ -7095,11 +7095,11 @@
       <c r="A340" s="5" t="n"/>
       <c r="B340" s="5" t="n"/>
       <c r="C340" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B340,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B340,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D340" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B340,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B340,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E340" s="8" t="n"/>
@@ -7114,11 +7114,11 @@
       <c r="A341" s="5" t="n"/>
       <c r="B341" s="5" t="n"/>
       <c r="C341" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B341,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B341,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D341" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B341,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B341,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E341" s="8" t="n"/>
@@ -7133,11 +7133,11 @@
       <c r="A342" s="5" t="n"/>
       <c r="B342" s="5" t="n"/>
       <c r="C342" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B342,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B342,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D342" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B342,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B342,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E342" s="8" t="n"/>
@@ -7152,11 +7152,11 @@
       <c r="A343" s="5" t="n"/>
       <c r="B343" s="5" t="n"/>
       <c r="C343" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B343,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B343,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D343" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B343,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B343,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E343" s="8" t="n"/>
@@ -7171,11 +7171,11 @@
       <c r="A344" s="5" t="n"/>
       <c r="B344" s="5" t="n"/>
       <c r="C344" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B344,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B344,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D344" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B344,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B344,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E344" s="8" t="n"/>
@@ -7190,11 +7190,11 @@
       <c r="A345" s="5" t="n"/>
       <c r="B345" s="5" t="n"/>
       <c r="C345" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B345,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B345,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D345" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B345,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B345,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E345" s="8" t="n"/>
@@ -7209,11 +7209,11 @@
       <c r="A346" s="5" t="n"/>
       <c r="B346" s="5" t="n"/>
       <c r="C346" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B346,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B346,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D346" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B346,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B346,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E346" s="8" t="n"/>
@@ -7228,11 +7228,11 @@
       <c r="A347" s="5" t="n"/>
       <c r="B347" s="5" t="n"/>
       <c r="C347" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B347,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B347,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D347" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B347,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B347,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E347" s="8" t="n"/>
@@ -7247,11 +7247,11 @@
       <c r="A348" s="5" t="n"/>
       <c r="B348" s="5" t="n"/>
       <c r="C348" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B348,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B348,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D348" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B348,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B348,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E348" s="8" t="n"/>
@@ -7266,11 +7266,11 @@
       <c r="A349" s="5" t="n"/>
       <c r="B349" s="5" t="n"/>
       <c r="C349" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B349,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B349,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D349" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B349,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B349,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E349" s="8" t="n"/>
@@ -7285,11 +7285,11 @@
       <c r="A350" s="5" t="n"/>
       <c r="B350" s="5" t="n"/>
       <c r="C350" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B350,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B350,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D350" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B350,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B350,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E350" s="8" t="n"/>
@@ -7304,11 +7304,11 @@
       <c r="A351" s="5" t="n"/>
       <c r="B351" s="5" t="n"/>
       <c r="C351" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B351,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B351,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D351" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B351,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B351,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E351" s="8" t="n"/>
@@ -7323,11 +7323,11 @@
       <c r="A352" s="5" t="n"/>
       <c r="B352" s="5" t="n"/>
       <c r="C352" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B352,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B352,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D352" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B352,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B352,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E352" s="8" t="n"/>
@@ -7342,11 +7342,11 @@
       <c r="A353" s="5" t="n"/>
       <c r="B353" s="5" t="n"/>
       <c r="C353" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B353,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B353,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D353" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B353,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B353,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E353" s="8" t="n"/>
@@ -7361,11 +7361,11 @@
       <c r="A354" s="5" t="n"/>
       <c r="B354" s="5" t="n"/>
       <c r="C354" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B354,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B354,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D354" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B354,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B354,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E354" s="8" t="n"/>
@@ -7380,11 +7380,11 @@
       <c r="A355" s="5" t="n"/>
       <c r="B355" s="5" t="n"/>
       <c r="C355" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B355,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B355,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D355" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B355,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B355,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E355" s="8" t="n"/>
@@ -7399,11 +7399,11 @@
       <c r="A356" s="5" t="n"/>
       <c r="B356" s="5" t="n"/>
       <c r="C356" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B356,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B356,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D356" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B356,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B356,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E356" s="8" t="n"/>
@@ -7418,11 +7418,11 @@
       <c r="A357" s="5" t="n"/>
       <c r="B357" s="5" t="n"/>
       <c r="C357" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B357,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B357,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D357" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B357,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B357,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E357" s="8" t="n"/>
@@ -7437,11 +7437,11 @@
       <c r="A358" s="5" t="n"/>
       <c r="B358" s="5" t="n"/>
       <c r="C358" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B358,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B358,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D358" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B358,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B358,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E358" s="8" t="n"/>
@@ -7456,11 +7456,11 @@
       <c r="A359" s="5" t="n"/>
       <c r="B359" s="5" t="n"/>
       <c r="C359" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B359,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B359,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D359" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B359,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B359,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E359" s="8" t="n"/>
@@ -7475,11 +7475,11 @@
       <c r="A360" s="5" t="n"/>
       <c r="B360" s="5" t="n"/>
       <c r="C360" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B360,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B360,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D360" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B360,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B360,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E360" s="8" t="n"/>
@@ -7494,11 +7494,11 @@
       <c r="A361" s="5" t="n"/>
       <c r="B361" s="5" t="n"/>
       <c r="C361" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B361,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B361,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D361" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B361,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B361,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E361" s="8" t="n"/>
@@ -7513,11 +7513,11 @@
       <c r="A362" s="5" t="n"/>
       <c r="B362" s="5" t="n"/>
       <c r="C362" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B362,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B362,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D362" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B362,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B362,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E362" s="8" t="n"/>
@@ -7532,11 +7532,11 @@
       <c r="A363" s="5" t="n"/>
       <c r="B363" s="5" t="n"/>
       <c r="C363" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B363,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B363,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D363" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B363,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B363,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E363" s="8" t="n"/>
@@ -7551,11 +7551,11 @@
       <c r="A364" s="5" t="n"/>
       <c r="B364" s="5" t="n"/>
       <c r="C364" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B364,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B364,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D364" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B364,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B364,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E364" s="8" t="n"/>
@@ -7570,11 +7570,11 @@
       <c r="A365" s="5" t="n"/>
       <c r="B365" s="5" t="n"/>
       <c r="C365" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B365,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B365,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D365" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B365,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B365,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E365" s="8" t="n"/>
@@ -7589,11 +7589,11 @@
       <c r="A366" s="5" t="n"/>
       <c r="B366" s="5" t="n"/>
       <c r="C366" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B366,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B366,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D366" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B366,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B366,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E366" s="8" t="n"/>
@@ -7608,11 +7608,11 @@
       <c r="A367" s="5" t="n"/>
       <c r="B367" s="5" t="n"/>
       <c r="C367" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B367,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B367,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D367" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B367,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B367,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E367" s="8" t="n"/>
@@ -7627,11 +7627,11 @@
       <c r="A368" s="5" t="n"/>
       <c r="B368" s="5" t="n"/>
       <c r="C368" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B368,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B368,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D368" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B368,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B368,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E368" s="8" t="n"/>
@@ -7646,11 +7646,11 @@
       <c r="A369" s="5" t="n"/>
       <c r="B369" s="5" t="n"/>
       <c r="C369" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B369,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B369,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D369" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B369,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B369,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E369" s="8" t="n"/>
@@ -7665,11 +7665,11 @@
       <c r="A370" s="5" t="n"/>
       <c r="B370" s="5" t="n"/>
       <c r="C370" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B370,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B370,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D370" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B370,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B370,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E370" s="8" t="n"/>
@@ -7684,11 +7684,11 @@
       <c r="A371" s="5" t="n"/>
       <c r="B371" s="5" t="n"/>
       <c r="C371" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B371,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B371,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D371" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B371,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B371,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E371" s="8" t="n"/>
@@ -7703,11 +7703,11 @@
       <c r="A372" s="5" t="n"/>
       <c r="B372" s="5" t="n"/>
       <c r="C372" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B372,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B372,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D372" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B372,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B372,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E372" s="8" t="n"/>
@@ -7722,11 +7722,11 @@
       <c r="A373" s="5" t="n"/>
       <c r="B373" s="5" t="n"/>
       <c r="C373" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B373,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B373,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D373" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B373,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B373,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E373" s="8" t="n"/>
@@ -7741,11 +7741,11 @@
       <c r="A374" s="5" t="n"/>
       <c r="B374" s="5" t="n"/>
       <c r="C374" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B374,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B374,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D374" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B374,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B374,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E374" s="8" t="n"/>
@@ -7760,11 +7760,11 @@
       <c r="A375" s="5" t="n"/>
       <c r="B375" s="5" t="n"/>
       <c r="C375" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B375,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B375,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D375" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B375,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B375,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E375" s="8" t="n"/>
@@ -7779,11 +7779,11 @@
       <c r="A376" s="5" t="n"/>
       <c r="B376" s="5" t="n"/>
       <c r="C376" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B376,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B376,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D376" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B376,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B376,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E376" s="8" t="n"/>
@@ -7798,11 +7798,11 @@
       <c r="A377" s="5" t="n"/>
       <c r="B377" s="5" t="n"/>
       <c r="C377" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B377,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B377,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D377" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B377,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B377,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E377" s="8" t="n"/>
@@ -7817,11 +7817,11 @@
       <c r="A378" s="5" t="n"/>
       <c r="B378" s="5" t="n"/>
       <c r="C378" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B378,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B378,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D378" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B378,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B378,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E378" s="8" t="n"/>
@@ -7836,11 +7836,11 @@
       <c r="A379" s="5" t="n"/>
       <c r="B379" s="5" t="n"/>
       <c r="C379" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B379,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B379,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D379" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B379,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B379,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E379" s="8" t="n"/>
@@ -7855,11 +7855,11 @@
       <c r="A380" s="5" t="n"/>
       <c r="B380" s="5" t="n"/>
       <c r="C380" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B380,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B380,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D380" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B380,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B380,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E380" s="8" t="n"/>
@@ -7874,11 +7874,11 @@
       <c r="A381" s="5" t="n"/>
       <c r="B381" s="5" t="n"/>
       <c r="C381" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B381,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B381,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D381" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B381,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B381,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E381" s="8" t="n"/>
@@ -7893,11 +7893,11 @@
       <c r="A382" s="5" t="n"/>
       <c r="B382" s="5" t="n"/>
       <c r="C382" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B382,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B382,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D382" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B382,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B382,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E382" s="8" t="n"/>
@@ -7912,11 +7912,11 @@
       <c r="A383" s="5" t="n"/>
       <c r="B383" s="5" t="n"/>
       <c r="C383" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B383,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B383,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D383" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B383,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B383,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E383" s="8" t="n"/>
@@ -7931,11 +7931,11 @@
       <c r="A384" s="5" t="n"/>
       <c r="B384" s="5" t="n"/>
       <c r="C384" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B384,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B384,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D384" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B384,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B384,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E384" s="8" t="n"/>
@@ -7950,11 +7950,11 @@
       <c r="A385" s="5" t="n"/>
       <c r="B385" s="5" t="n"/>
       <c r="C385" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B385,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B385,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D385" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B385,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B385,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E385" s="8" t="n"/>
@@ -7969,11 +7969,11 @@
       <c r="A386" s="5" t="n"/>
       <c r="B386" s="5" t="n"/>
       <c r="C386" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B386,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B386,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D386" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B386,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B386,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E386" s="8" t="n"/>
@@ -7988,11 +7988,11 @@
       <c r="A387" s="5" t="n"/>
       <c r="B387" s="5" t="n"/>
       <c r="C387" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B387,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B387,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D387" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B387,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B387,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E387" s="8" t="n"/>
@@ -8007,11 +8007,11 @@
       <c r="A388" s="5" t="n"/>
       <c r="B388" s="5" t="n"/>
       <c r="C388" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B388,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B388,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D388" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B388,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B388,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E388" s="8" t="n"/>
@@ -8026,11 +8026,11 @@
       <c r="A389" s="5" t="n"/>
       <c r="B389" s="5" t="n"/>
       <c r="C389" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B389,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B389,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D389" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B389,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B389,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E389" s="8" t="n"/>
@@ -8045,11 +8045,11 @@
       <c r="A390" s="5" t="n"/>
       <c r="B390" s="5" t="n"/>
       <c r="C390" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B390,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B390,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D390" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B390,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B390,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E390" s="8" t="n"/>
@@ -8064,11 +8064,11 @@
       <c r="A391" s="5" t="n"/>
       <c r="B391" s="5" t="n"/>
       <c r="C391" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B391,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B391,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D391" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B391,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B391,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E391" s="8" t="n"/>
@@ -8083,11 +8083,11 @@
       <c r="A392" s="5" t="n"/>
       <c r="B392" s="5" t="n"/>
       <c r="C392" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B392,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B392,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D392" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B392,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B392,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E392" s="8" t="n"/>
@@ -8102,11 +8102,11 @@
       <c r="A393" s="5" t="n"/>
       <c r="B393" s="5" t="n"/>
       <c r="C393" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B393,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B393,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D393" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B393,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B393,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E393" s="8" t="n"/>
@@ -8121,11 +8121,11 @@
       <c r="A394" s="5" t="n"/>
       <c r="B394" s="5" t="n"/>
       <c r="C394" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B394,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B394,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D394" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B394,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B394,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E394" s="8" t="n"/>
@@ -8140,11 +8140,11 @@
       <c r="A395" s="5" t="n"/>
       <c r="B395" s="5" t="n"/>
       <c r="C395" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B395,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B395,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D395" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B395,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B395,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E395" s="8" t="n"/>
@@ -8159,11 +8159,11 @@
       <c r="A396" s="5" t="n"/>
       <c r="B396" s="5" t="n"/>
       <c r="C396" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B396,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B396,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D396" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B396,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B396,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E396" s="8" t="n"/>
@@ -8178,11 +8178,11 @@
       <c r="A397" s="5" t="n"/>
       <c r="B397" s="5" t="n"/>
       <c r="C397" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B397,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B397,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D397" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B397,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B397,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E397" s="8" t="n"/>
@@ -8197,11 +8197,11 @@
       <c r="A398" s="5" t="n"/>
       <c r="B398" s="5" t="n"/>
       <c r="C398" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B398,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B398,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D398" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B398,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B398,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E398" s="8" t="n"/>
@@ -8216,11 +8216,11 @@
       <c r="A399" s="5" t="n"/>
       <c r="B399" s="5" t="n"/>
       <c r="C399" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B399,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B399,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D399" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B399,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B399,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E399" s="8" t="n"/>
@@ -8235,11 +8235,11 @@
       <c r="A400" s="5" t="n"/>
       <c r="B400" s="5" t="n"/>
       <c r="C400" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B400,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B400,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D400" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B400,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B400,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E400" s="8" t="n"/>
@@ -8254,11 +8254,11 @@
       <c r="A401" s="5" t="n"/>
       <c r="B401" s="5" t="n"/>
       <c r="C401" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B401,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B401,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D401" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B401,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B401,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E401" s="8" t="n"/>
@@ -8273,11 +8273,11 @@
       <c r="A402" s="5" t="n"/>
       <c r="B402" s="5" t="n"/>
       <c r="C402" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$865,MATCH(B402,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$864,MATCH(B402,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="D402" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$865,MATCH(B402,Productos!$A$2:$A$865,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$864,MATCH(B402,Productos!$A$2:$A$864,0)),"")</f>
         <v/>
       </c>
       <c r="E402" s="8" t="n"/>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>D SMARTBONES POLLO MEDIANO 2UD · 93515690000</t>
+          <t>D SMARTBONES POLLO MINI 8CT · 93515610000</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -10562,11 +10562,6 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>ROYAL CANI ADULTO YORKSHIRE 1.5 KG. · 90401970000</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>D SMARTBONES POLLO MINI 8CT · 93515610000</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -13698,7 +13693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D869"/>
+  <dimension ref="A1:D868"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14755,7 +14750,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -14855,7 +14850,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -14975,7 +14970,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -15175,7 +15170,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -15315,7 +15310,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -15875,7 +15870,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -15895,7 +15890,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -16315,7 +16310,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -17395,7 +17390,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -17415,7 +17410,7 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19115,7 +19110,7 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19135,7 +19130,7 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19235,7 +19230,7 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19995,7 +19990,7 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20955,7 +20950,7 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21215,7 +21210,7 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -21515,7 +21510,7 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -21655,7 +21650,7 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -21675,7 +21670,7 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -21695,7 +21690,7 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -21715,7 +21710,7 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -21775,7 +21770,7 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -21795,7 +21790,7 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -21815,7 +21810,7 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -21835,7 +21830,7 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -21855,7 +21850,7 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -21875,7 +21870,7 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -21895,7 +21890,7 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -21975,7 +21970,7 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -22235,7 +22230,7 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -22415,7 +22410,7 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -22435,7 +22430,7 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -22935,7 +22930,7 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -23295,7 +23290,7 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -23475,7 +23470,7 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -23555,7 +23550,7 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -23655,7 +23650,7 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -23855,7 +23850,7 @@
         </is>
       </c>
       <c r="C508" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -24515,7 +24510,7 @@
         </is>
       </c>
       <c r="C541" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -24535,7 +24530,7 @@
         </is>
       </c>
       <c r="C542" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -25655,7 +25650,7 @@
         </is>
       </c>
       <c r="C598" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -26175,7 +26170,7 @@
         </is>
       </c>
       <c r="C624" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -26415,7 +26410,7 @@
         </is>
       </c>
       <c r="C636" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -26675,7 +26670,7 @@
         </is>
       </c>
       <c r="C649" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -26735,7 +26730,7 @@
         </is>
       </c>
       <c r="C652" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -27035,7 +27030,7 @@
         </is>
       </c>
       <c r="C667" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -27055,7 +27050,7 @@
         </is>
       </c>
       <c r="C668" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -27075,7 +27070,7 @@
         </is>
       </c>
       <c r="C669" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -27235,7 +27230,7 @@
         </is>
       </c>
       <c r="C677" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -27335,7 +27330,7 @@
         </is>
       </c>
       <c r="C682" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -27635,7 +27630,7 @@
         </is>
       </c>
       <c r="C697" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -27855,7 +27850,7 @@
         </is>
       </c>
       <c r="C708" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -28035,7 +28030,7 @@
         </is>
       </c>
       <c r="C717" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -28355,7 +28350,7 @@
         </is>
       </c>
       <c r="C733" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -28555,7 +28550,7 @@
         </is>
       </c>
       <c r="C743" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -28746,16 +28741,16 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>D SMARTBONES POLLO MEDIANO 2UD · 93515690000</t>
+          <t>D SMARTBONES POLLO MINI 8CT · 93515610000</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>93515690000</t>
+          <t>93515610000</t>
         </is>
       </c>
       <c r="C753" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -28766,36 +28761,36 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>D SMARTBONES POLLO MINI 8CT · 93515610000</t>
+          <t>D SE JALEA PARA AVES 20OZ · 93517930000</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>93515610000</t>
+          <t>93517930000</t>
         </is>
       </c>
       <c r="C754" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>SMARTBONES</t>
+          <t>SONGBIRD ESSENTIALS</t>
         </is>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>D SE JALEA PARA AVES 20OZ · 93517930000</t>
+          <t>D SE NECTAR PARA MARIPOSAS 5OZ · 93517920000</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>93517930000</t>
+          <t>93517920000</t>
         </is>
       </c>
       <c r="C755" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -28806,36 +28801,36 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>D SE NECTAR PARA MARIPOSAS 5OZ · 93517920000</t>
+          <t>SUPER GATO 1.5KG · 93500000800</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>93517920000</t>
+          <t>93500000800</t>
         </is>
       </c>
       <c r="C756" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>SONGBIRD ESSENTIALS</t>
+          <t>SUPER GATO</t>
         </is>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>SUPER GATO 1.5KG · 93500000800</t>
+          <t>SUPER GATO 500GRS · 93500000700</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>93500000800</t>
+          <t>93500000700</t>
         </is>
       </c>
       <c r="C757" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -28846,16 +28841,16 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>SUPER GATO 500GRS · 93500000700</t>
+          <t>SUPER GATO 8KG · 93500000900</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>93500000700</t>
+          <t>93500000900</t>
         </is>
       </c>
       <c r="C758" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -28866,36 +28861,36 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>SUPER GATO 8KG · 93500000900</t>
+          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>93500000900</t>
+          <t>90022370000</t>
         </is>
       </c>
       <c r="C759" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>SUPER GATO</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
+          <t>ROCKY ADULTOS 1KG · 93500000342</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>90022370000</t>
+          <t>93500000342</t>
         </is>
       </c>
       <c r="C760" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -28906,16 +28901,16 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 1KG · 93500000342</t>
+          <t>ROCKY ADULTOS 4KG · 93500000343</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>93500000342</t>
+          <t>93500000343</t>
         </is>
       </c>
       <c r="C761" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -28926,16 +28921,16 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 4KG · 93500000343</t>
+          <t>ROCKY ADULTOS 500G · 93500000341</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>93500000343</t>
+          <t>93500000341</t>
         </is>
       </c>
       <c r="C762" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -28946,16 +28941,16 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 500G · 93500000341</t>
+          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>93500000341</t>
+          <t>93511670000</t>
         </is>
       </c>
       <c r="C763" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -28966,16 +28961,16 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
+          <t>SUPERKAN HUESOS D JAMON SERRANO 3UD · 93505430000</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>93511670000</t>
+          <t>93505430000</t>
         </is>
       </c>
       <c r="C764" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -28986,36 +28981,36 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>SUPERKAN HUESOS D JAMON SERRANO 3UD · 93505430000</t>
+          <t>D SUPRA SNACK ROLLITOS D CARNE · 93509310000</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>93505430000</t>
+          <t>93509310000</t>
         </is>
       </c>
       <c r="C765" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>D SUPRA SNACK ROLLITOS D CARNE · 93509310000</t>
+          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>93509310000</t>
+          <t>93509320000</t>
         </is>
       </c>
       <c r="C766" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -29026,16 +29021,16 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
+          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>93509320000</t>
+          <t>93508860000</t>
         </is>
       </c>
       <c r="C767" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -29046,16 +29041,16 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
+          <t>SUPRA ADULTO 18KG · 93508890000</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>93508860000</t>
+          <t>93508890000</t>
         </is>
       </c>
       <c r="C768" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -29066,16 +29061,16 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 18KG · 93508890000</t>
+          <t>SUPRA ADULTO 30KG · 93508900000</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>93508890000</t>
+          <t>93508900000</t>
         </is>
       </c>
       <c r="C769" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -29086,16 +29081,16 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 30KG · 93508900000</t>
+          <t>SUPRA ADULTO 4KG · 93508870000</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>93508900000</t>
+          <t>93508870000</t>
         </is>
       </c>
       <c r="C770" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -29106,16 +29101,16 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 4KG · 93508870000</t>
+          <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>93508870000</t>
+          <t>93508910000</t>
         </is>
       </c>
       <c r="C771" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -29126,16 +29121,16 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
+          <t>SUPRA CACHORRO 4KG · 93508920000</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>93508910000</t>
+          <t>93508920000</t>
         </is>
       </c>
       <c r="C772" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -29146,56 +29141,56 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 4KG · 93508920000</t>
+          <t>D SHED-X SUPLEMENTO NUTRI /GATOS · 90329820000</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>93508920000</t>
+          <t>90329820000</t>
         </is>
       </c>
       <c r="C773" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>SYNERGY</t>
         </is>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>D SHED-X SUPLEMENTO NUTRI /GATOS · 90329820000</t>
+          <t>TOW ARROYO ANTIGUO CON SALMÓN AHUMADO 2, · 90013320000</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>90329820000</t>
+          <t>90013320000</t>
         </is>
       </c>
       <c r="C774" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>SYNERGY</t>
+          <t>TASTE OF THE WILD</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>TOW ARROYO ANTIGUO CON SALMÓN AHUMADO 2, · 90013320000</t>
+          <t>TOW CAÑÓN SUROESTE CON JABALÍ 2KG · 90013340000</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>90013320000</t>
+          <t>90013340000</t>
         </is>
       </c>
       <c r="C775" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -29206,16 +29201,16 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>TOW CAÑÓN SUROESTE CON JABALÍ 2KG · 90013340000</t>
+          <t>TOW CAÑÓN SUROESTE CON JABALÍ 5.6KG · 90013260000</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>90013340000</t>
+          <t>90013260000</t>
         </is>
       </c>
       <c r="C776" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -29226,12 +29221,12 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>TOW CAÑÓN SUROESTE CON JABALÍ 5.6KG · 90013260000</t>
+          <t>TOW FELINA DE LAS MONTANAS ROCOSAS 6.6KG · 90013210000</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>90013260000</t>
+          <t>90013210000</t>
         </is>
       </c>
       <c r="C777" t="n">
@@ -29246,16 +29241,16 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>TOW FELINA DE LAS MONTANAS ROCOSAS 6.6KG · 90013210000</t>
+          <t>TOW FÓRMULA FELINA TRUCHA Y SALMÓN AHUMA · 90013380000</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>90013210000</t>
+          <t>90013380000</t>
         </is>
       </c>
       <c r="C778" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -29266,16 +29261,16 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>TOW FÓRMULA FELINA TRUCHA Y SALMÓN AHUMA · 90013380000</t>
+          <t>TOW HIGH  CACHORRO  BISONTE Y VENADO ASA · 90013280000</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>90013380000</t>
+          <t>90013280000</t>
         </is>
       </c>
       <c r="C779" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -29286,16 +29281,16 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>TOW HIGH  CACHORRO  BISONTE Y VENADO ASA · 90013280000</t>
+          <t>TOW HIGH PRAIRIE BISONTE VENADO  12.2KG · 90013170000</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>90013280000</t>
+          <t>90013170000</t>
         </is>
       </c>
       <c r="C780" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -29306,16 +29301,16 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>TOW HIGH PRAIRIE BISONTE VENADO  12.2KG · 90013170000</t>
+          <t>TOW HIGH PRAIRIE CON BISONTE Y VENADO AS · 90013390000</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>90013170000</t>
+          <t>90013390000</t>
         </is>
       </c>
       <c r="C781" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -29326,16 +29321,16 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>TOW HIGH PRAIRIE CON BISONTE Y VENADO AS · 90013390000</t>
+          <t>TOW HUMEDALES CANINOS CON AVES SILVESTRE · 90013270000</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>90013390000</t>
+          <t>90013270000</t>
         </is>
       </c>
       <c r="C782" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -29346,16 +29341,16 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>TOW HUMEDALES CANINOS CON AVES SILVESTRE · 90013270000</t>
+          <t>TOW HUMEDALES CANINOS CON AVES SILVESTRE · 90013330000</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>90013270000</t>
+          <t>90013330000</t>
         </is>
       </c>
       <c r="C783" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -29366,16 +29361,16 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>TOW HUMEDALES CANINOS CON AVES SILVESTRE · 90013330000</t>
+          <t>TOW LOWLAND CREEK CON CODORNICES ASADAS · 90013410000</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>90013330000</t>
+          <t>90013410000</t>
         </is>
       </c>
       <c r="C784" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -29386,16 +29381,16 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>TOW LOWLAND CREEK CON CODORNICES ASADAS · 90013410000</t>
+          <t>TOW PACIFIC CACHORRO  SALMÓN AHUMADO 2KG · 90013370000</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>90013410000</t>
+          <t>90013370000</t>
         </is>
       </c>
       <c r="C785" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -29406,16 +29401,16 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>TOW PACIFIC CACHORRO  SALMÓN AHUMADO 2KG · 90013370000</t>
+          <t>TOW PACIFIC CACHORRO SALMÓN AHUMADO 5.6K · 90013300000</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>90013370000</t>
+          <t>90013300000</t>
         </is>
       </c>
       <c r="C786" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -29426,16 +29421,16 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>TOW PACIFIC CACHORRO SALMÓN AHUMADO 5.6K · 90013300000</t>
+          <t>TOW PACIFIC S SALMON AHUMAD 12.2 KG · 90013230000</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>90013300000</t>
+          <t>90013230000</t>
         </is>
       </c>
       <c r="C787" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -29446,12 +29441,12 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>TOW PACIFIC S SALMON AHUMAD 12.2 KG · 90013230000</t>
+          <t>TOW PACIFIC ST CACHORRO SALMON 12.2 KG · 90013180000</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>90013230000</t>
+          <t>90013180000</t>
         </is>
       </c>
       <c r="C788" t="n">
@@ -29466,16 +29461,16 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>TOW PACIFIC ST CACHORRO SALMON 12.2 KG · 90013180000</t>
+          <t>TOW PACIFIC STREAM CON SALMÓN AHUMADO 5. · 90013250000</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>90013180000</t>
+          <t>90013250000</t>
         </is>
       </c>
       <c r="C789" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -29486,16 +29481,16 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>TOW PACIFIC STREAM CON SALMÓN AHUMADO 5. · 90013250000</t>
+          <t>TOW PINAR CON CIERVO Y LEGUMBRES 2KG · 90013350000</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>90013250000</t>
+          <t>90013350000</t>
         </is>
       </c>
       <c r="C790" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -29506,16 +29501,16 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>TOW PINAR CON CIERVO Y LEGUMBRES 2KG · 90013350000</t>
+          <t>TOW PINAR CON CIERVO Y LEGUMBRES 2KG · 90013360000</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>90013350000</t>
+          <t>90013360000</t>
         </is>
       </c>
       <c r="C791" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -29526,16 +29521,16 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>TOW PINAR CON CIERVO Y LEGUMBRES 2KG · 90013360000</t>
+          <t>TOW SIERRA MONTA CORDERO ASADO 12.2KG · 90013190000</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>90013360000</t>
+          <t>90013190000</t>
         </is>
       </c>
       <c r="C792" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -29546,16 +29541,16 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>TOW SIERRA MONTA CORDERO ASADO 12.2KG · 90013190000</t>
+          <t>TOW SIERRA MONTAÑA CON CORDERO ASADO 5.6 · 90013290000</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>90013190000</t>
+          <t>90013290000</t>
         </is>
       </c>
       <c r="C793" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -29566,36 +29561,36 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>TOW SIERRA MONTAÑA CON CORDERO ASADO 5.6 · 90013290000</t>
+          <t>D TETRA ALIMENTO COMUNITARIO 3.25OZ · 93518690000</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>90013290000</t>
+          <t>93518690000</t>
         </is>
       </c>
       <c r="C794" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>TASTE OF THE WILD</t>
+          <t>TETRA</t>
         </is>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>D TETRA ALIMENTO COMUNITARIO 3.25OZ · 93518690000</t>
+          <t>D TETRA REPTOMIN 1.94 OZ · 90410040000</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>93518690000</t>
+          <t>90410040000</t>
         </is>
       </c>
       <c r="C795" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -29606,16 +29601,16 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>D TETRA REPTOMIN 1.94 OZ · 90410040000</t>
+          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>90410040000</t>
+          <t>90409640000</t>
         </is>
       </c>
       <c r="C796" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -29626,16 +29621,16 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
+          <t>TETRA ALGAE WAFER 2COLOR 12OZ · 90313380000</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>90409640000</t>
+          <t>90313380000</t>
         </is>
       </c>
       <c r="C797" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -29646,16 +29641,16 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>TETRA ALGAE WAFER 2COLOR 12OZ · 90313380000</t>
+          <t>TETRA ALIMENTO BETTA WORMS 0.98OZ · 93518650000</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>90313380000</t>
+          <t>93518650000</t>
         </is>
       </c>
       <c r="C798" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -29666,16 +29661,16 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>TETRA ALIMENTO BETTA WORMS 0.98OZ · 93518650000</t>
+          <t>TETRA BETTAMIN .81OZ  23GR · 90410310000</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>93518650000</t>
+          <t>90410310000</t>
         </is>
       </c>
       <c r="C799" t="n">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -29686,16 +29681,16 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>TETRA BETTAMIN .81OZ  23GR · 90410310000</t>
+          <t>TETRA GEL FIN DE SEMANA 2 UD 24G · 90407210000</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>90410310000</t>
+          <t>90407210000</t>
         </is>
       </c>
       <c r="C800" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -29706,16 +29701,16 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>TETRA GEL FIN DE SEMANA 2 UD 24G · 90407210000</t>
+          <t>TETRA HOJUELA GOLDFISH 2.2OZ · 90409670000</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>90407210000</t>
+          <t>90409670000</t>
         </is>
       </c>
       <c r="C801" t="n">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -29726,16 +29721,16 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>TETRA HOJUELA GOLDFISH 2.2OZ · 90409670000</t>
+          <t>TETRA HOJUELAS GOLDFISH .42OZ · 90409900000</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>90409670000</t>
+          <t>90409900000</t>
         </is>
       </c>
       <c r="C802" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -29746,16 +29741,16 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>TETRA HOJUELAS GOLDFISH .42OZ · 90409900000</t>
+          <t>TETRA HOJUELAS GOLDFISH 3.53OZ · 90409910000</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>90409900000</t>
+          <t>90409910000</t>
         </is>
       </c>
       <c r="C803" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -29766,16 +29761,16 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>TETRA HOJUELAS GOLDFISH 3.53OZ · 90409910000</t>
+          <t>TETRA HOJUELAS TROPICAL 0.42OZ · 90409920000</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>90409910000</t>
+          <t>90409920000</t>
         </is>
       </c>
       <c r="C804" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -29786,16 +29781,16 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>TETRA HOJUELAS TROPICAL 0.42OZ · 90409920000</t>
+          <t>TETRA POND STICKS 2.53 LB · 90402260000</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>90409920000</t>
+          <t>90402260000</t>
         </is>
       </c>
       <c r="C805" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -29806,16 +29801,16 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>TETRA POND STICKS 2.53 LB · 90402260000</t>
+          <t>TETRA REPTOMINPRO TORTUGA JOVEN 12 · 93518680000</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>90402260000</t>
+          <t>93518680000</t>
         </is>
       </c>
       <c r="C806" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -29826,16 +29821,16 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>TETRA REPTOMINPRO TORTUGA JOVEN 12 · 93518680000</t>
+          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>93518680000</t>
+          <t>90410990000</t>
         </is>
       </c>
       <c r="C807" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -29846,16 +29841,16 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
+          <t>TETRAFIN HOJUELAS GOLDFISH 7.06 OZ · 90410490000</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>90410990000</t>
+          <t>90410490000</t>
         </is>
       </c>
       <c r="C808" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -29866,16 +29861,16 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>TETRAFIN HOJUELAS GOLDFISH 7.06 OZ · 90410490000</t>
+          <t>TETRAFIN PELLET FLOTANTE 1.87OZ · 90410020000</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>90410490000</t>
+          <t>90410020000</t>
         </is>
       </c>
       <c r="C809" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -29886,16 +29881,16 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>TETRAFIN PELLET FLOTANTE 1.87OZ · 90410020000</t>
+          <t>TETRAMIN HOJUELAS 2.2OZ  62GR · 90410290000</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>90410020000</t>
+          <t>90410290000</t>
         </is>
       </c>
       <c r="C810" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -29906,16 +29901,16 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>TETRAMIN HOJUELAS 2.2OZ  62GR · 90410290000</t>
+          <t>TETRAMIN HOJUELAS 3.53 OZ. · 90720600000</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>90410290000</t>
+          <t>90720600000</t>
         </is>
       </c>
       <c r="C811" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -29926,16 +29921,16 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>TETRAMIN HOJUELAS 3.53 OZ. · 90720600000</t>
+          <t>TETRAMIN HOJUELAS PEZ TROPICAL1OZ · 90410980000</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>90720600000</t>
+          <t>90410980000</t>
         </is>
       </c>
       <c r="C812" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -29946,36 +29941,36 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>TETRAMIN HOJUELAS PEZ TROPICAL1OZ · 90410980000</t>
+          <t>D TRIUMPH CAT CAFE SALMON Y TUNA 30LB · 935096300001</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>90410980000</t>
+          <t>935096300001</t>
         </is>
       </c>
       <c r="C813" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>TRIUMPH</t>
         </is>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>D TRIUMPH CAT CAFE SALMON Y TUNA 30LB · 935096300001</t>
+          <t>D TRIUMPH SNACK P/PERROS CARNE JERKY · 90762830000</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>935096300001</t>
+          <t>90762830000</t>
         </is>
       </c>
       <c r="C814" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -29986,16 +29981,16 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>D TRIUMPH SNACK P/PERROS CARNE JERKY · 90762830000</t>
+          <t>TRIUMPH FS GRAIN FREE SALMON 26L · 93501390000</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>90762830000</t>
+          <t>93501390000</t>
         </is>
       </c>
       <c r="C815" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -30006,16 +30001,16 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>TRIUMPH FS GRAIN FREE SALMON 26L · 93501390000</t>
+          <t>TRIUMPH FS GRAIN FREE SALMON 3LB · 93501370000</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>93501390000</t>
+          <t>93501370000</t>
         </is>
       </c>
       <c r="C816" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -30026,36 +30021,36 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>TRIUMPH FS GRAIN FREE SALMON 3LB · 93501370000</t>
+          <t>C VET LIFE NAT GASTROINTESTINAL 2 KG · 90010010000</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>93501370000</t>
+          <t>90010010000</t>
         </is>
       </c>
       <c r="C817" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>TRIUMPH</t>
+          <t>VET LIFE</t>
         </is>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>C VET LIFE NAT GASTROINTESTINAL 2 KG · 90010010000</t>
+          <t>C VET LIFE NAT RENAL 2 KG · 90010050000</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>90010010000</t>
+          <t>90010050000</t>
         </is>
       </c>
       <c r="C818" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -30066,16 +30061,16 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>C VET LIFE NAT RENAL 2 KG · 90010050000</t>
+          <t>C VET LIFE URI STRUVITE 2 KG · 90010070000</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>90010050000</t>
+          <t>90010070000</t>
         </is>
       </c>
       <c r="C819" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -30086,16 +30081,16 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>C VET LIFE URI STRUVITE 2 KG · 90010070000</t>
+          <t>F VET LIFE NAT OBESIDAD 2 KG · 90010130000</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>90010070000</t>
+          <t>90010130000</t>
         </is>
       </c>
       <c r="C820" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -30106,36 +30101,36 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>F VET LIFE NAT OBESIDAD 2 KG · 90010130000</t>
+          <t>WHISKAS  POUCH ATUN SARDINA 85GR. · 90028540000</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>90010130000</t>
+          <t>90028540000</t>
         </is>
       </c>
       <c r="C821" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>VET LIFE</t>
+          <t>WHISKAS</t>
         </is>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>WHISKAS  POUCH ATUN SARDINA 85GR. · 90028540000</t>
+          <t>WHISKAS CARNE ORIGINAL 1.5KG · 90408360000</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>90028540000</t>
+          <t>90408360000</t>
         </is>
       </c>
       <c r="C822" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -30146,16 +30141,16 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>WHISKAS CARNE ORIGINAL 1.5KG · 90408360000</t>
+          <t>WHISKAS CARNE ORIGINAL 3KG · 90028490000</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>90408360000</t>
+          <t>90028490000</t>
         </is>
       </c>
       <c r="C823" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -30166,16 +30161,16 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>WHISKAS CARNE ORIGINAL 3KG · 90028490000</t>
+          <t>WHISKAS GATITOS 1.4KG · 93515190000</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>90028490000</t>
+          <t>93515190000</t>
         </is>
       </c>
       <c r="C824" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -30186,16 +30181,16 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>WHISKAS GATITOS 1.4KG · 93515190000</t>
+          <t>WHISKAS ORIGINAL SABOR CARNE 500G · 93518270000</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>93515190000</t>
+          <t>93518270000</t>
         </is>
       </c>
       <c r="C825" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -30206,16 +30201,16 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>WHISKAS ORIGINAL SABOR CARNE 500G · 93518270000</t>
+          <t>WHISKAS PESCADO 1.5KG · 90301130000</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>93518270000</t>
+          <t>90301130000</t>
         </is>
       </c>
       <c r="C826" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -30226,16 +30221,16 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>WHISKAS PESCADO 1.5KG · 90301130000</t>
+          <t>WHISKAS POLLO 1.5KG · 90408380000</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>90301130000</t>
+          <t>90408380000</t>
         </is>
       </c>
       <c r="C827" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -30246,16 +30241,16 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>WHISKAS POLLO 1.5KG · 90408380000</t>
+          <t>WHISKAS POUCH ATÚN 85GR. · 90028530000</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>90408380000</t>
+          <t>90028530000</t>
         </is>
       </c>
       <c r="C828" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -30266,16 +30261,16 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH ATÚN 85GR. · 90028530000</t>
+          <t>WHISKAS POUCH PARRIMIXTA 85GR. · 90028520000</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>90028530000</t>
+          <t>90028520000</t>
         </is>
       </c>
       <c r="C829" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -30286,16 +30281,16 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH PARRIMIXTA 85GR. · 90028520000</t>
+          <t>WHISKAS POUCH POLLO 85GR · 90409050000</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>90028520000</t>
+          <t>90409050000</t>
         </is>
       </c>
       <c r="C830" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -30306,16 +30301,16 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH POLLO 85GR · 90409050000</t>
+          <t>WHISKAS POUCH POLLO Y PAVO 85GR. · 90028550000</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>90409050000</t>
+          <t>90028550000</t>
         </is>
       </c>
       <c r="C831" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -30326,16 +30321,16 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH POLLO Y PAVO 85GR. · 90028550000</t>
+          <t>WHISKAS POUCH RES  85GR · 90409070000</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>90028550000</t>
+          <t>90409070000</t>
         </is>
       </c>
       <c r="C832" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -30346,32 +30341,32 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH RES  85GR · 90409070000</t>
+          <t>D ZM ALIM GOURMET TORTUGA TERRESTR 12 · 93517610000</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>90409070000</t>
+          <t>93517610000</t>
         </is>
       </c>
       <c r="C833" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>WHISKAS</t>
+          <t>ZOO MED</t>
         </is>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>D ZM ALIM GOURMET TORTUGA TERRESTR 12 · 93517610000</t>
+          <t>D ZM ALIM GOURMET/ TORTUGA TERRESTRE · 93517600000</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>93517610000</t>
+          <t>93517600000</t>
         </is>
       </c>
       <c r="C834" t="n">
@@ -30386,16 +30381,16 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>D ZM ALIM GOURMET/ TORTUGA TERRESTRE · 93517600000</t>
+          <t>D ZM ALIM P/GRILLOS 1.75OZ · 90415490000</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>93517600000</t>
+          <t>90415490000</t>
         </is>
       </c>
       <c r="C835" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -30406,16 +30401,16 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>D ZM ALIM P/GRILLOS 1.75OZ · 90415490000</t>
+          <t>D ZM ALIM TORTUGA TERREST NATURAL 340 · 90415990000</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>90415490000</t>
+          <t>90415990000</t>
         </is>
       </c>
       <c r="C836" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -30426,16 +30421,16 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>D ZM ALIM TORTUGA TERREST NATURAL 340 · 90415990000</t>
+          <t>D ZM ALIMENTO EN BLOQUE P TORTUGAS 1 · 93517500000</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>90415990000</t>
+          <t>93517500000</t>
         </is>
       </c>
       <c r="C837" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -30446,16 +30441,16 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>D ZM ALIMENTO EN BLOQUE P TORTUGAS 1 · 93517500000</t>
+          <t>D ZM ALIMENTO EN BLOQUE P TORTUGAS 5 · 93517490000</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>93517500000</t>
+          <t>93517490000</t>
         </is>
       </c>
       <c r="C838" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -30466,16 +30461,16 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>D ZM ALIMENTO EN BLOQUE P TORTUGAS 5 · 93517490000</t>
+          <t>D ZM ALIMENTO EN BLOQUES P/BETTAS · 93514820000</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>93517490000</t>
+          <t>93514820000</t>
         </is>
       </c>
       <c r="C839" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -30486,16 +30481,16 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>D ZM ALIMENTO EN BLOQUES P/BETTAS · 93514820000</t>
+          <t>D ZM ALIMENTO VARIADO P BETTA 0.12OZ · 93504390000</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>93514820000</t>
+          <t>93504390000</t>
         </is>
       </c>
       <c r="C840" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -30506,16 +30501,16 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>D ZM ALIMENTO VARIADO P BETTA 0.12OZ · 93504390000</t>
+          <t>D ZM CALCIO PARA AVES 3OZ · 93514810000</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>93504390000</t>
+          <t>93514810000</t>
         </is>
       </c>
       <c r="C841" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -30526,16 +30521,16 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>D ZM CALCIO PARA AVES 3OZ · 93514810000</t>
+          <t>D ZM DRAGON BARBUDO ADULTO 10OZ. · 90415500000</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>93514810000</t>
+          <t>90415500000</t>
         </is>
       </c>
       <c r="C842" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -30546,12 +30541,12 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>D ZM DRAGON BARBUDO ADULTO 10OZ. · 90415500000</t>
+          <t>D ZM DRAGON BARBUDO JOVEN 2OZ. · 90415480000</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>90415500000</t>
+          <t>90415480000</t>
         </is>
       </c>
       <c r="C843" t="n">
@@ -30566,16 +30561,16 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>D ZM DRAGON BARBUDO JOVEN 2OZ. · 90415480000</t>
+          <t>D ZM SNACK DE FLORES P/LAGARTIJAS 6G · 93517660000</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>90415480000</t>
+          <t>93517660000</t>
         </is>
       </c>
       <c r="C844" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -30586,16 +30581,16 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>D ZM SNACK DE FLORES P/LAGARTIJAS 6G · 93517660000</t>
+          <t>D ZM SUPLEMENTO VITAMINICO P/AVES · 93514800000</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>93517660000</t>
+          <t>93514800000</t>
         </is>
       </c>
       <c r="C845" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -30606,16 +30601,16 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>D ZM SUPLEMENTO VITAMINICO P/AVES · 93514800000</t>
+          <t>ZM ALIM NATURAL FONDO P/TORTUGA 2.1 · 93517580000</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>93514800000</t>
+          <t>93517580000</t>
         </is>
       </c>
       <c r="C846" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -30626,16 +30621,16 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>ZM ALIM NATURAL FONDO P/TORTUGA 2.1 · 93517580000</t>
+          <t>ZM ALIM NATURAL TORTUGA ACUATICA 12 · 93517630000</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>93517580000</t>
+          <t>93517630000</t>
         </is>
       </c>
       <c r="C847" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -30646,16 +30641,16 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>ZM ALIM NATURAL TORTUGA ACUATICA 12 · 93517630000</t>
+          <t>ZM ALIM NATURAL TORTUGA ACUATICA 7 · 93517560000</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>93517630000</t>
+          <t>93517560000</t>
         </is>
       </c>
       <c r="C848" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -30666,16 +30661,16 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>ZM ALIM NATURAL TORTUGA ACUATICA 7 · 93517560000</t>
+          <t>ZM ALIM TORTUGA GOURMET 6OZ · 90415950000</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>93517560000</t>
+          <t>90415950000</t>
         </is>
       </c>
       <c r="C849" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -30686,16 +30681,16 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>ZM ALIM TORTUGA GOURMET 6OZ · 90415950000</t>
+          <t>ZM ALIM TORTUGA NATURAL 184GR · 90415940000</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>90415950000</t>
+          <t>90415940000</t>
         </is>
       </c>
       <c r="C850" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -30706,16 +30701,16 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>ZM ALIM TORTUGA NATURAL 184GR · 90415940000</t>
+          <t>ZM ALIM TORTUGAS REPTISTICKS 141GR · 90415930000</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>90415940000</t>
+          <t>90415930000</t>
         </is>
       </c>
       <c r="C851" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -30726,16 +30721,16 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>ZM ALIM TORTUGAS REPTISTICKS 141GR · 90415930000</t>
+          <t>ZM ALIM TORTUGAS REPTISTICKS 28GR · 90415880000</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>90415930000</t>
+          <t>90415880000</t>
         </is>
       </c>
       <c r="C852" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -30746,16 +30741,16 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>ZM ALIM TORTUGAS REPTISTICKS 28GR · 90415880000</t>
+          <t>ZM ALIMENTO EN BLOQUE PARA PECES 1 · 93517470000</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>90415880000</t>
+          <t>93517470000</t>
         </is>
       </c>
       <c r="C853" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -30766,16 +30761,16 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>ZM ALIMENTO EN BLOQUE PARA PECES 1 · 93517470000</t>
+          <t>ZM ALIMENTO EN BLOQUE PARA PECES 6 · 93517480000</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>93517470000</t>
+          <t>93517480000</t>
         </is>
       </c>
       <c r="C854" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -30786,16 +30781,16 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>ZM ALIMENTO EN BLOQUE PARA PECES 6 · 93517480000</t>
+          <t>ZM ALIMENTO EN GEL P INSECTOS 3 · 93517520000</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>93517480000</t>
+          <t>93517520000</t>
         </is>
       </c>
       <c r="C855" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -30806,16 +30801,16 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>ZM ALIMENTO EN GEL P INSECTOS 3 · 93517520000</t>
+          <t>ZM ALIMENTO EN PELLET P INSECTOS 4G · 93517530000</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>93517520000</t>
+          <t>93517530000</t>
         </is>
       </c>
       <c r="C856" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -30826,16 +30821,16 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>ZM ALIMENTO EN PELLET P INSECTOS 4G · 93517530000</t>
+          <t>ZM ALIMENTO GOURMET P TORTUGAS 4.5 · 93517540000</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>93517530000</t>
+          <t>93517540000</t>
         </is>
       </c>
       <c r="C857" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -30846,16 +30841,16 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>ZM ALIMENTO GOURMET P TORTUGAS 4.5 · 93517540000</t>
+          <t>ZM ALIMENTO GOURMET P TORTUGAS 8.5 · 93517550000</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>93517540000</t>
+          <t>93517550000</t>
         </is>
       </c>
       <c r="C858" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -30866,16 +30861,16 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>ZM ALIMENTO GOURMET P TORTUGAS 8.5 · 93517550000</t>
+          <t>ZM ALIMENTO P/TORTUGA ACUAT 425G · 90410650000</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>93517550000</t>
+          <t>90410650000</t>
         </is>
       </c>
       <c r="C859" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -30886,16 +30881,16 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>ZM ALIMENTO P/TORTUGA ACUAT 425G · 90410650000</t>
+          <t>ZM ALIMENTO TORTUGA ACUATICA  52G · 90410660000</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>90410650000</t>
+          <t>90410660000</t>
         </is>
       </c>
       <c r="C860" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -30906,16 +30901,16 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>ZM ALIMENTO TORTUGA ACUATICA  52G · 90410660000</t>
+          <t>ZM CALCIO PQNO CON VEGETALES P/AVES · 93503060000</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>90410660000</t>
+          <t>93503060000</t>
         </is>
       </c>
       <c r="C861" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -30926,16 +30921,16 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>ZM CALCIO PQNO CON VEGETALES P/AVES · 93503060000</t>
+          <t>ZM ELECTROLITOS PARA REPTILES 8OZ · 93519210000</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>93503060000</t>
+          <t>93519210000</t>
         </is>
       </c>
       <c r="C862" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -30946,16 +30941,16 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>ZM ELECTROLITOS PARA REPTILES 8OZ · 93519210000</t>
+          <t>ZM MICRO PELLET P/BETTA 0.12OZ · 93514830000</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>93519210000</t>
+          <t>93514830000</t>
         </is>
       </c>
       <c r="C863" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -30966,16 +30961,16 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>ZM MICRO PELLET P/BETTA 0.12OZ · 93514830000</t>
+          <t>ZM MICRO PELLETS P/BETTAS 0.65OZ · 93514840000</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>93514830000</t>
+          <t>93514840000</t>
         </is>
       </c>
       <c r="C864" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -30983,57 +30978,37 @@
         </is>
       </c>
     </row>
-    <row r="865">
-      <c r="A865" t="inlineStr">
-        <is>
-          <t>ZM MICRO PELLETS P/BETTAS 0.65OZ · 93514840000</t>
-        </is>
-      </c>
-      <c r="B865" t="inlineStr">
-        <is>
-          <t>93514840000</t>
-        </is>
-      </c>
-      <c r="C865" t="n">
-        <v>29</v>
-      </c>
-      <c r="D865" t="inlineStr">
-        <is>
-          <t>ZOO MED</t>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>P&amp;G | LA CHORRERA</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>Sucursal</t>
-        </is>
-      </c>
-      <c r="B867" t="inlineStr">
-        <is>
-          <t>P&amp;G | LA CHORRERA</t>
-        </is>
+          <t>Índice</t>
+        </is>
+      </c>
+      <c r="B867" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>Índice</t>
-        </is>
-      </c>
-      <c r="B868" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="869">
-      <c r="A869" t="inlineStr">
-        <is>
           <t>Inventario al</t>
         </is>
       </c>
-      <c r="B869" t="inlineStr">
-        <is>
-          <t>20.10.2026</t>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
         </is>
       </c>
     </row>
